--- a/docs/Sunny Diamonds Test Cases .xlsx
+++ b/docs/Sunny Diamonds Test Cases .xlsx
@@ -9,6 +9,9 @@
     <sheet name="PLP" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="wishlist" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Blogs" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Blogs Gap Tracker" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Contact Us" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Contact Us Issues" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Login Registration'!$A$1:$F$39</definedName>
@@ -57669,56 +57672,56 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>Module:</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>Blogs</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>Routes:</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="0" t="inlineStr">
         <is>
           <t>/blogs, /blogs/[slug]</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>Data Source:</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>Strapi CMS (blogPosts, blogLandingPage, blogCategories)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>ISR:</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>revalidate = 300 (5 min)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>Pagination:</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>BLOGS_INITIAL_VISIBLE = 9, BLOGS_LOAD_MORE_STEP = 3</t>
         </is>
@@ -57744,60 +57747,60 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="0" t="inlineStr">
         <is>
           <t>PRE-01</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>Strapi CMS is reachable with published blog posts</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="0" t="inlineStr">
         <is>
           <t>PRE-02</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>At least 10+ published posts across multiple categories</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="0" t="inlineStr">
         <is>
           <t>PRE-03</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>Blog landing page configured in CMS (hero, optional featured post)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="0" t="inlineStr">
         <is>
           <t>PRE-04</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>Test on Desktop (&gt;=1280px), Tablet (~768px), Mobile (&lt;=390px)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="0" t="inlineStr">
         <is>
           <t>PRE-05</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>Browsers: Chrome, Safari, Firefox, Edge (latest)</t>
         </is>
@@ -57823,72 +57826,72 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="0" t="inlineStr">
         <is>
           <t>Post A</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="0" t="inlineStr">
         <is>
           <t>Full HTML body, multiple H2s, hero + cover, author, read time, category bridal, tags</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="0" t="inlineStr">
         <is>
           <t>Post B</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="0" t="inlineStr">
         <is>
           <t>Markdown body with bullets, image row, no hero image</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="0" t="inlineStr">
         <is>
           <t>Post C</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="0" t="inlineStr">
         <is>
           <t>Minimal post (title + slug only)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="0" t="inlineStr">
         <is>
           <t>Post D–L</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="0" t="inlineStr">
         <is>
           <t>10+ posts across categories for load-more testing</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="0" t="inlineStr">
         <is>
           <t>Landing config</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="0" t="inlineStr">
         <is>
           <t>Hero images (desktop + mobile), featured post, SEO fields</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="0" t="inlineStr">
         <is>
           <t>Empty category</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="0" t="inlineStr">
         <is>
           <t>Category with 0 posts (or filter yielding none)</t>
         </is>
@@ -57902,42 +57905,42 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="0" t="inlineStr">
         <is>
           <t>• Blog search — not implemented</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="0" t="inlineStr">
         <is>
           <t>• Breadcrumbs — not implemented</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="0" t="inlineStr">
         <is>
           <t>• Tag chips on cards/detail — not implemented</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="0" t="inlineStr">
         <is>
           <t>• Dedicated loading.tsx / error.tsx under /blogs — not implemented</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="0" t="inlineStr">
         <is>
           <t>• User-visible API error/retry UI on listing failure — not implemented</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="0" t="inlineStr">
         <is>
           <t>• Server-side pagination — all posts fetched up to 100; client paginates 9+3</t>
         </is>
@@ -65614,4 +65617,8025 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K56"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" style="41" min="1" max="1"/>
+    <col width="12" customWidth="1" style="41" min="2" max="2"/>
+    <col width="14" customWidth="1" style="41" min="3" max="3"/>
+    <col width="42" customWidth="1" style="41" min="4" max="4"/>
+    <col width="42" customWidth="1" style="41" min="5" max="5"/>
+    <col width="10" customWidth="1" style="41" min="6" max="6"/>
+    <col width="10" customWidth="1" style="41" min="7" max="7"/>
+    <col width="8" customWidth="1" style="41" min="8" max="8"/>
+    <col width="14" customWidth="1" style="41" min="9" max="9"/>
+    <col width="12" customWidth="1" style="41" min="10" max="10"/>
+    <col width="30" customWidth="1" style="41" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="42" t="inlineStr">
+        <is>
+          <t>BLOGS MODULE — GAP TRACKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>Source Spec:</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/document/d/1MbDZpiq93Ua2DGo5Bq-1qjU2H9bp4TsfnAsvc9lEZyU/edit?tab=t.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>Spec Version:</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>Blog_Module_Functional_Technical_Specification_v1.1</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>Audit Date:</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="42" t="inlineStr">
+        <is>
+          <t>STATUS SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B6" s="43" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="42" t="inlineStr">
+        <is>
+          <t>SEVERITY SUMMARY (OPEN GAPS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="43" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="B13" s="43" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="42" t="inlineStr">
+        <is>
+          <t>GAP ITEMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="43" t="inlineStr">
+        <is>
+          <t>Gap ID</t>
+        </is>
+      </c>
+      <c r="B19" s="43" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="C19" s="43" t="inlineStr">
+        <is>
+          <t>Spec Section</t>
+        </is>
+      </c>
+      <c r="D19" s="43" t="inlineStr">
+        <is>
+          <t>Spec Requirement</t>
+        </is>
+      </c>
+      <c r="E19" s="43" t="inlineStr">
+        <is>
+          <t>Current Implementation</t>
+        </is>
+      </c>
+      <c r="F19" s="43" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G19" s="43" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="H19" s="43" t="inlineStr">
+        <is>
+          <t>Effort</t>
+        </is>
+      </c>
+      <c r="I19" s="43" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="J19" s="43" t="inlineStr">
+        <is>
+          <t>Jira</t>
+        </is>
+      </c>
+      <c r="K19" s="43" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="44" t="inlineStr">
+        <is>
+          <t>BLOG-GAP-001</t>
+        </is>
+      </c>
+      <c r="B20" s="44" t="inlineStr">
+        <is>
+          <t>Landing</t>
+        </is>
+      </c>
+      <c r="C20" s="44" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="D20" s="44" t="inlineStr">
+        <is>
+          <t>Category row labeled "Explore Topics"</t>
+        </is>
+      </c>
+      <c r="E20" s="44" t="inlineStr">
+        <is>
+          <t>Label is "Filter by:"</t>
+        </is>
+      </c>
+      <c r="F20" s="44" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="G20" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H20" s="44" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I20" s="44" t="inlineStr"/>
+      <c r="J20" s="44" t="inlineStr"/>
+      <c r="K20" s="44" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="44" t="inlineStr">
+        <is>
+          <t>BLOG-GAP-002</t>
+        </is>
+      </c>
+      <c r="B21" s="44" t="inlineStr">
+        <is>
+          <t>Landing</t>
+        </is>
+      </c>
+      <c r="C21" s="44" t="inlineStr">
+        <is>
+          <t>1.1 / 1.2</t>
+        </is>
+      </c>
+      <c r="D21" s="44" t="inlineStr">
+        <is>
+          <t>Load More appends 9 posts per click</t>
+        </is>
+      </c>
+      <c r="E21" s="44" t="inlineStr">
+        <is>
+          <t>Appends 3 (BLOGS_LOAD_MORE_STEP = 3)</t>
+        </is>
+      </c>
+      <c r="F21" s="44" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G21" s="44" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H21" s="44" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I21" s="44" t="inlineStr"/>
+      <c r="J21" s="44" t="inlineStr"/>
+      <c r="K21" s="44" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="44" t="inlineStr">
+        <is>
+          <t>BLOG-GAP-003</t>
+        </is>
+      </c>
+      <c r="B22" s="44" t="inlineStr">
+        <is>
+          <t>Landing</t>
+        </is>
+      </c>
+      <c r="C22" s="44" t="inlineStr">
+        <is>
+          <t>1.3 #4</t>
+        </is>
+      </c>
+      <c r="D22" s="44" t="inlineStr">
+        <is>
+          <t>API returns posts in batches of 9 for load more</t>
+        </is>
+      </c>
+      <c r="E22" s="44" t="inlineStr">
+        <is>
+          <t>All posts fetched once (pageSize=100); client-only pagination</t>
+        </is>
+      </c>
+      <c r="F22" s="44" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="G22" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H22" s="44" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I22" s="44" t="inlineStr"/>
+      <c r="J22" s="44" t="inlineStr"/>
+      <c r="K22" s="44" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="44" t="inlineStr">
+        <is>
+          <t>BLOG-GAP-004</t>
+        </is>
+      </c>
+      <c r="B23" s="44" t="inlineStr">
+        <is>
+          <t>Landing</t>
+        </is>
+      </c>
+      <c r="C23" s="44" t="inlineStr">
+        <is>
+          <t>1.2 #2</t>
+        </is>
+      </c>
+      <c r="D23" s="44" t="inlineStr">
+        <is>
+          <t>Featured post deduplicated from regular grid</t>
+        </is>
+      </c>
+      <c r="E23" s="44" t="inlineStr">
+        <is>
+          <t>Featured post remains in posts array — can appear twice</t>
+        </is>
+      </c>
+      <c r="F23" s="44" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G23" s="44" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H23" s="44" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I23" s="44" t="inlineStr"/>
+      <c r="J23" s="44" t="inlineStr"/>
+      <c r="K23" s="44" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="44" t="inlineStr">
+        <is>
+          <t>BLOG-GAP-005</t>
+        </is>
+      </c>
+      <c r="B24" s="44" t="inlineStr">
+        <is>
+          <t>Landing</t>
+        </is>
+      </c>
+      <c r="C24" s="44" t="inlineStr">
+        <is>
+          <t>1.1 Pagination</t>
+        </is>
+      </c>
+      <c r="D24" s="44" t="inlineStr">
+        <is>
+          <t>Initial load: 9 regular + 1 featured (10 total, no duplicate)</t>
+        </is>
+      </c>
+      <c r="E24" s="44" t="inlineStr">
+        <is>
+          <t>9 grid slots shown but featured may duplicate in grid</t>
+        </is>
+      </c>
+      <c r="F24" s="44" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G24" s="44" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H24" s="44" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I24" s="44" t="inlineStr"/>
+      <c r="J24" s="44" t="inlineStr"/>
+      <c r="K24" s="44" t="inlineStr">
+        <is>
+          <t>Related to BLOG-GAP-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="44" t="inlineStr">
+        <is>
+          <t>BLOG-GAP-006</t>
+        </is>
+      </c>
+      <c r="B25" s="44" t="inlineStr">
+        <is>
+          <t>Landing</t>
+        </is>
+      </c>
+      <c r="C25" s="44" t="inlineStr">
+        <is>
+          <t>1.1 Featured</t>
+        </is>
+      </c>
+      <c r="D25" s="44" t="inlineStr">
+        <is>
+          <t>Featured cutout image separate from background</t>
+        </is>
+      </c>
+      <c r="E25" s="44" t="inlineStr">
+        <is>
+          <t>Uses cover image; cutoutImage not mapped</t>
+        </is>
+      </c>
+      <c r="F25" s="44" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="G25" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H25" s="44" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I25" s="44" t="inlineStr"/>
+      <c r="J25" s="44" t="inlineStr"/>
+      <c r="K25" s="44" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="44" t="inlineStr">
+        <is>
+          <t>BLOG-GAP-007</t>
+        </is>
+      </c>
+      <c r="B26" s="44" t="inlineStr">
+        <is>
+          <t>Landing</t>
+        </is>
+      </c>
+      <c r="C26" s="44" t="inlineStr">
+        <is>
+          <t>1.3 #1</t>
+        </is>
+      </c>
+      <c r="D26" s="44" t="inlineStr">
+        <is>
+          <t>Categories from CMS taxonomy only</t>
+        </is>
+      </c>
+      <c r="E26" s="44" t="inlineStr">
+        <is>
+          <t>Inferred categories from title/excerpt/tags when CMS missing</t>
+        </is>
+      </c>
+      <c r="F26" s="44" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="G26" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H26" s="44" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I26" s="44" t="inlineStr"/>
+      <c r="J26" s="44" t="inlineStr"/>
+      <c r="K26" s="44" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="44" t="inlineStr">
+        <is>
+          <t>BLOG-GAP-008</t>
+        </is>
+      </c>
+      <c r="B27" s="44" t="inlineStr">
+        <is>
+          <t>Landing</t>
+        </is>
+      </c>
+      <c r="C27" s="44" t="inlineStr">
+        <is>
+          <t>1.2 #5</t>
+        </is>
+      </c>
+      <c r="D27" s="44" t="inlineStr">
+        <is>
+          <t>Category filter re-queries backend</t>
+        </is>
+      </c>
+      <c r="E27" s="44" t="inlineStr">
+        <is>
+          <t>Client-side filter on preloaded list</t>
+        </is>
+      </c>
+      <c r="F27" s="44" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="G27" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H27" s="44" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I27" s="44" t="inlineStr"/>
+      <c r="J27" s="44" t="inlineStr"/>
+      <c r="K27" s="44" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="44" t="inlineStr">
+        <is>
+          <t>BLOG-GAP-009</t>
+        </is>
+      </c>
+      <c r="B28" s="44" t="inlineStr">
+        <is>
+          <t>Landing</t>
+        </is>
+      </c>
+      <c r="C28" s="44" t="inlineStr">
+        <is>
+          <t>1.2 #1</t>
+        </is>
+      </c>
+      <c r="D28" s="44" t="inlineStr">
+        <is>
+          <t>Featured hidden → grid reflows with no gap</t>
+        </is>
+      </c>
+      <c r="E28" s="44" t="inlineStr">
+        <is>
+          <t>Grid OK, but duplicate featured breaks layout intent</t>
+        </is>
+      </c>
+      <c r="F28" s="44" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="G28" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H28" s="44" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I28" s="44" t="inlineStr"/>
+      <c r="J28" s="44" t="inlineStr"/>
+      <c r="K28" s="44" t="inlineStr">
+        <is>
+          <t>Fix with BLOG-GAP-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="44" t="inlineStr">
+        <is>
+          <t>BLOG-GAP-010</t>
+        </is>
+      </c>
+      <c r="B29" s="44" t="inlineStr">
+        <is>
+          <t>Landing</t>
+        </is>
+      </c>
+      <c r="C29" s="44" t="inlineStr">
+        <is>
+          <t>1.1 Banner</t>
+        </is>
+      </c>
+      <c r="D29" s="44" t="inlineStr">
+        <is>
+          <t>Static hero banner, no carousel</t>
+        </is>
+      </c>
+      <c r="E29" s="44" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="F29" s="44" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G29" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H29" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I29" s="44" t="inlineStr"/>
+      <c r="J29" s="44" t="inlineStr"/>
+      <c r="K29" s="44" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="44" t="inlineStr">
+        <is>
+          <t>BLOG-GAP-011</t>
+        </is>
+      </c>
+      <c r="B30" s="44" t="inlineStr">
+        <is>
+          <t>Landing</t>
+        </is>
+      </c>
+      <c r="C30" s="44" t="inlineStr">
+        <is>
+          <t>1.1 Cards</t>
+        </is>
+      </c>
+      <c r="D30" s="44" t="inlineStr">
+        <is>
+          <t>3 cards per row, fully clickable</t>
+        </is>
+      </c>
+      <c r="E30" s="44" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="F30" s="44" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G30" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H30" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I30" s="44" t="inlineStr"/>
+      <c r="J30" s="44" t="inlineStr"/>
+      <c r="K30" s="44" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="44" t="inlineStr">
+        <is>
+          <t>BLOG-GAP-012</t>
+        </is>
+      </c>
+      <c r="B31" s="44" t="inlineStr">
+        <is>
+          <t>Landing</t>
+        </is>
+      </c>
+      <c r="C31" s="44" t="inlineStr">
+        <is>
+          <t>1.1 Cards</t>
+        </is>
+      </c>
+      <c r="D31" s="44" t="inlineStr">
+        <is>
+          <t>Title, date, min-read on cards</t>
+        </is>
+      </c>
+      <c r="E31" s="44" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="F31" s="44" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G31" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H31" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I31" s="44" t="inlineStr"/>
+      <c r="J31" s="44" t="inlineStr"/>
+      <c r="K31" s="44" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="44" t="inlineStr">
+        <is>
+          <t>BLOG-GAP-013</t>
+        </is>
+      </c>
+      <c r="B32" s="44" t="inlineStr">
+        <is>
+          <t>Landing</t>
+        </is>
+      </c>
+      <c r="C32" s="44" t="inlineStr">
+        <is>
+          <t>1.1 Cards</t>
+        </is>
+      </c>
+      <c r="D32" s="44" t="inlineStr">
+        <is>
+          <t>Latest date first</t>
+        </is>
+      </c>
+      <c r="E32" s="44" t="inlineStr">
+        <is>
+          <t>publishedDate:desc</t>
+        </is>
+      </c>
+      <c r="F32" s="44" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G32" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H32" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I32" s="44" t="inlineStr"/>
+      <c r="J32" s="44" t="inlineStr"/>
+      <c r="K32" s="44" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="44" t="inlineStr">
+        <is>
+          <t>BLOG-GAP-014</t>
+        </is>
+      </c>
+      <c r="B33" s="44" t="inlineStr">
+        <is>
+          <t>Landing</t>
+        </is>
+      </c>
+      <c r="C33" s="44" t="inlineStr">
+        <is>
+          <t>1.1 Featured</t>
+        </is>
+      </c>
+      <c r="D33" s="44" t="inlineStr">
+        <is>
+          <t>Featured after first row of 3</t>
+        </is>
+      </c>
+      <c r="E33" s="44" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="F33" s="44" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G33" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H33" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I33" s="44" t="inlineStr"/>
+      <c r="J33" s="44" t="inlineStr"/>
+      <c r="K33" s="44" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="44" t="inlineStr">
+        <is>
+          <t>BLOG-GAP-015</t>
+        </is>
+      </c>
+      <c r="B34" s="44" t="inlineStr">
+        <is>
+          <t>Landing</t>
+        </is>
+      </c>
+      <c r="C34" s="44" t="inlineStr">
+        <is>
+          <t>1.3 #3</t>
+        </is>
+      </c>
+      <c r="D34" s="44" t="inlineStr">
+        <is>
+          <t>Featured via landing featuredBlog, not post flag</t>
+        </is>
+      </c>
+      <c r="E34" s="44" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="F34" s="44" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G34" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H34" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I34" s="44" t="inlineStr"/>
+      <c r="J34" s="44" t="inlineStr"/>
+      <c r="K34" s="44" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="44" t="inlineStr">
+        <is>
+          <t>BLOG-GAP-016</t>
+        </is>
+      </c>
+      <c r="B35" s="44" t="inlineStr">
+        <is>
+          <t>Landing</t>
+        </is>
+      </c>
+      <c r="C35" s="44" t="inlineStr">
+        <is>
+          <t>1.1 Featured</t>
+        </is>
+      </c>
+      <c r="D35" s="44" t="inlineStr">
+        <is>
+          <t>Featured background from landing section</t>
+        </is>
+      </c>
+      <c r="E35" s="44" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="F35" s="44" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G35" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H35" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I35" s="44" t="inlineStr"/>
+      <c r="J35" s="44" t="inlineStr"/>
+      <c r="K35" s="44" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="44" t="inlineStr">
+        <is>
+          <t>BLOG-GAP-017</t>
+        </is>
+      </c>
+      <c r="B36" s="44" t="inlineStr">
+        <is>
+          <t>Landing</t>
+        </is>
+      </c>
+      <c r="C36" s="44" t="inlineStr">
+        <is>
+          <t>1.2 #3</t>
+        </is>
+      </c>
+      <c r="D36" s="44" t="inlineStr">
+        <is>
+          <t>Featured always shows Excerpt</t>
+        </is>
+      </c>
+      <c r="E36" s="44" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="F36" s="44" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G36" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H36" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I36" s="44" t="inlineStr"/>
+      <c r="J36" s="44" t="inlineStr"/>
+      <c r="K36" s="44" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="44" t="inlineStr">
+        <is>
+          <t>BLOG-GAP-018</t>
+        </is>
+      </c>
+      <c r="B37" s="44" t="inlineStr">
+        <is>
+          <t>Landing</t>
+        </is>
+      </c>
+      <c r="C37" s="44" t="inlineStr">
+        <is>
+          <t>1.2 #5</t>
+        </is>
+      </c>
+      <c r="D37" s="44" t="inlineStr">
+        <is>
+          <t>Category change resets to first page</t>
+        </is>
+      </c>
+      <c r="E37" s="44" t="inlineStr">
+        <is>
+          <t>setLimit(9) on category change</t>
+        </is>
+      </c>
+      <c r="F37" s="44" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G37" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H37" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I37" s="44" t="inlineStr"/>
+      <c r="J37" s="44" t="inlineStr"/>
+      <c r="K37" s="44" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="44" t="inlineStr">
+        <is>
+          <t>BLOG-GAP-019</t>
+        </is>
+      </c>
+      <c r="B38" s="44" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="C38" s="44" t="inlineStr">
+        <is>
+          <t>2.1 Hero</t>
+        </is>
+      </c>
+      <c r="D38" s="44" t="inlineStr">
+        <is>
+          <t>Title, author, date, min-read backend-driven</t>
+        </is>
+      </c>
+      <c r="E38" s="44" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="F38" s="44" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G38" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H38" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I38" s="44" t="inlineStr"/>
+      <c r="J38" s="44" t="inlineStr"/>
+      <c r="K38" s="44" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="44" t="inlineStr">
+        <is>
+          <t>BLOG-GAP-020</t>
+        </is>
+      </c>
+      <c r="B39" s="44" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="C39" s="44" t="inlineStr">
+        <is>
+          <t>2.1 Hero</t>
+        </is>
+      </c>
+      <c r="D39" s="44" t="inlineStr">
+        <is>
+          <t>Cover image mobile + desktop separate assets</t>
+        </is>
+      </c>
+      <c r="E39" s="44" t="inlineStr">
+        <is>
+          <t>Single heroImage.src (desktop preferred)</t>
+        </is>
+      </c>
+      <c r="F39" s="44" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="G39" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H39" s="44" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I39" s="44" t="inlineStr"/>
+      <c r="J39" s="44" t="inlineStr"/>
+      <c r="K39" s="44" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="44" t="inlineStr">
+        <is>
+          <t>BLOG-GAP-021</t>
+        </is>
+      </c>
+      <c r="B40" s="44" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="C40" s="44" t="inlineStr">
+        <is>
+          <t>2.1 Content</t>
+        </is>
+      </c>
+      <c r="D40" s="44" t="inlineStr">
+        <is>
+          <t>HTML/rich-text body rendered as-is</t>
+        </is>
+      </c>
+      <c r="E40" s="44" t="inlineStr">
+        <is>
+          <t>Implemented (sanitized)</t>
+        </is>
+      </c>
+      <c r="F40" s="44" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G40" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H40" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I40" s="44" t="inlineStr"/>
+      <c r="J40" s="44" t="inlineStr"/>
+      <c r="K40" s="44" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="44" t="inlineStr">
+        <is>
+          <t>BLOG-GAP-022</t>
+        </is>
+      </c>
+      <c r="B41" s="44" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="C41" s="44" t="inlineStr">
+        <is>
+          <t>2.1 TOC</t>
+        </is>
+      </c>
+      <c r="D41" s="44" t="inlineStr">
+        <is>
+          <t>TOC from H2, sticky, scroll-linked</t>
+        </is>
+      </c>
+      <c r="E41" s="44" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="F41" s="44" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G41" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H41" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I41" s="44" t="inlineStr"/>
+      <c r="J41" s="44" t="inlineStr"/>
+      <c r="K41" s="44" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="44" t="inlineStr">
+        <is>
+          <t>BLOG-GAP-023</t>
+        </is>
+      </c>
+      <c r="B42" s="44" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="C42" s="44" t="inlineStr">
+        <is>
+          <t>2.2 #3</t>
+        </is>
+      </c>
+      <c r="D42" s="44" t="inlineStr">
+        <is>
+          <t>Desktop share → toast "Link copied"</t>
+        </is>
+      </c>
+      <c r="E42" s="44" t="inlineStr">
+        <is>
+          <t>Clipboard copy silent, no toast</t>
+        </is>
+      </c>
+      <c r="F42" s="44" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G42" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H42" s="44" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I42" s="44" t="inlineStr"/>
+      <c r="J42" s="44" t="inlineStr"/>
+      <c r="K42" s="44" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="44" t="inlineStr">
+        <is>
+          <t>BLOG-GAP-024</t>
+        </is>
+      </c>
+      <c r="B43" s="44" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="C43" s="44" t="inlineStr">
+        <is>
+          <t>2.2 #3</t>
+        </is>
+      </c>
+      <c r="D43" s="44" t="inlineStr">
+        <is>
+          <t>Mobile share → native share sheet</t>
+        </is>
+      </c>
+      <c r="E43" s="44" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="F43" s="44" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G43" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H43" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I43" s="44" t="inlineStr"/>
+      <c r="J43" s="44" t="inlineStr"/>
+      <c r="K43" s="44" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="44" t="inlineStr">
+        <is>
+          <t>BLOG-GAP-025</t>
+        </is>
+      </c>
+      <c r="B44" s="44" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="C44" s="44" t="inlineStr">
+        <is>
+          <t>2.2 #4</t>
+        </is>
+      </c>
+      <c r="D44" s="44" t="inlineStr">
+        <is>
+          <t>LISTEN / STOP via browser TTS</t>
+        </is>
+      </c>
+      <c r="E44" s="44" t="inlineStr">
+        <is>
+          <t>Implemented (uppercase labels)</t>
+        </is>
+      </c>
+      <c r="F44" s="44" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="G44" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H44" s="44" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I44" s="44" t="inlineStr"/>
+      <c r="J44" s="44" t="inlineStr"/>
+      <c r="K44" s="44" t="inlineStr">
+        <is>
+          <t>Label casing differs from spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="44" t="inlineStr">
+        <is>
+          <t>BLOG-GAP-026</t>
+        </is>
+      </c>
+      <c r="B45" s="44" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="C45" s="44" t="inlineStr">
+        <is>
+          <t>2.1 Tags</t>
+        </is>
+      </c>
+      <c r="D45" s="44" t="inlineStr">
+        <is>
+          <t>Tag UI — select tag shows all matching blogs</t>
+        </is>
+      </c>
+      <c r="E45" s="44" t="inlineStr">
+        <is>
+          <t>Tags internal only; no UI</t>
+        </is>
+      </c>
+      <c r="F45" s="44" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G45" s="44" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H45" s="44" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I45" s="44" t="inlineStr"/>
+      <c r="J45" s="44" t="inlineStr"/>
+      <c r="K45" s="44" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="44" t="inlineStr">
+        <is>
+          <t>BLOG-GAP-027</t>
+        </is>
+      </c>
+      <c r="B46" s="44" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="C46" s="44" t="inlineStr">
+        <is>
+          <t>2.2 #5</t>
+        </is>
+      </c>
+      <c r="D46" s="44" t="inlineStr">
+        <is>
+          <t>Related: closest tag match, then latest date</t>
+        </is>
+      </c>
+      <c r="E46" s="44" t="inlineStr">
+        <is>
+          <t>Category (+100) beats tags (+10)</t>
+        </is>
+      </c>
+      <c r="F46" s="44" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="G46" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H46" s="44" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I46" s="44" t="inlineStr"/>
+      <c r="J46" s="44" t="inlineStr"/>
+      <c r="K46" s="44" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="44" t="inlineStr">
+        <is>
+          <t>BLOG-GAP-028</t>
+        </is>
+      </c>
+      <c r="B47" s="44" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="C47" s="44" t="inlineStr">
+        <is>
+          <t>2.3 #7</t>
+        </is>
+      </c>
+      <c r="D47" s="44" t="inlineStr">
+        <is>
+          <t>Related: ≥1 shared tag, sorted date desc</t>
+        </is>
+      </c>
+      <c r="E47" s="44" t="inlineStr">
+        <is>
+          <t>Category can qualify without shared tags</t>
+        </is>
+      </c>
+      <c r="F47" s="44" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="G47" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H47" s="44" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I47" s="44" t="inlineStr"/>
+      <c r="J47" s="44" t="inlineStr"/>
+      <c r="K47" s="44" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="44" t="inlineStr">
+        <is>
+          <t>BLOG-GAP-029</t>
+        </is>
+      </c>
+      <c r="B48" s="44" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="C48" s="44" t="inlineStr">
+        <is>
+          <t>2.3 #8</t>
+        </is>
+      </c>
+      <c r="D48" s="44" t="inlineStr">
+        <is>
+          <t>Min-read: 200 words/min at API</t>
+        </is>
+      </c>
+      <c r="E48" s="44" t="inlineStr">
+        <is>
+          <t>Uses CMS readTimeMinutes/labels; no client calc</t>
+        </is>
+      </c>
+      <c r="F48" s="44" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="G48" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H48" s="44" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I48" s="44" t="inlineStr"/>
+      <c r="J48" s="44" t="inlineStr"/>
+      <c r="K48" s="44" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="44" t="inlineStr">
+        <is>
+          <t>BLOG-GAP-030</t>
+        </is>
+      </c>
+      <c r="B49" s="44" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="C49" s="44" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D49" s="44" t="inlineStr">
+        <is>
+          <t>More to Read — 3 cards with image, title, date, min-read</t>
+        </is>
+      </c>
+      <c r="E49" s="44" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="F49" s="44" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G49" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H49" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I49" s="44" t="inlineStr"/>
+      <c r="J49" s="44" t="inlineStr"/>
+      <c r="K49" s="44" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="44" t="inlineStr">
+        <is>
+          <t>BLOG-GAP-031</t>
+        </is>
+      </c>
+      <c r="B50" s="44" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="C50" s="44" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D50" s="44" t="inlineStr">
+        <is>
+          <t>Page title CMS-driven (listing + detail)</t>
+        </is>
+      </c>
+      <c r="E50" s="44" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="F50" s="44" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G50" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H50" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I50" s="44" t="inlineStr"/>
+      <c r="J50" s="44" t="inlineStr"/>
+      <c r="K50" s="44" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="44" t="inlineStr">
+        <is>
+          <t>BLOG-GAP-032</t>
+        </is>
+      </c>
+      <c r="B51" s="44" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="C51" s="44" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D51" s="44" t="inlineStr">
+        <is>
+          <t>Meta description CMS-driven</t>
+        </is>
+      </c>
+      <c r="E51" s="44" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="F51" s="44" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G51" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H51" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I51" s="44" t="inlineStr"/>
+      <c r="J51" s="44" t="inlineStr"/>
+      <c r="K51" s="44" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="44" t="inlineStr">
+        <is>
+          <t>BLOG-GAP-033</t>
+        </is>
+      </c>
+      <c r="B52" s="44" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="C52" s="44" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D52" s="44" t="inlineStr">
+        <is>
+          <t>Image alt tags CMS-editable</t>
+        </is>
+      </c>
+      <c r="E52" s="44" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="F52" s="44" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G52" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H52" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I52" s="44" t="inlineStr"/>
+      <c r="J52" s="44" t="inlineStr"/>
+      <c r="K52" s="44" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="44" t="inlineStr">
+        <is>
+          <t>BLOG-GAP-034</t>
+        </is>
+      </c>
+      <c r="B53" s="44" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="C53" s="44" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D53" s="44" t="inlineStr">
+        <is>
+          <t>Canonical URL per page</t>
+        </is>
+      </c>
+      <c r="E53" s="44" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="F53" s="44" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G53" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H53" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I53" s="44" t="inlineStr"/>
+      <c r="J53" s="44" t="inlineStr"/>
+      <c r="K53" s="44" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="44" t="inlineStr">
+        <is>
+          <t>BLOG-GAP-035</t>
+        </is>
+      </c>
+      <c r="B54" s="44" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="C54" s="44" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D54" s="44" t="inlineStr">
+        <is>
+          <t>Meta keywords CMS-editable</t>
+        </is>
+      </c>
+      <c r="E54" s="44" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="F54" s="44" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G54" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H54" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I54" s="44" t="inlineStr"/>
+      <c r="J54" s="44" t="inlineStr"/>
+      <c r="K54" s="44" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="44" t="inlineStr">
+        <is>
+          <t>BLOG-GAP-036</t>
+        </is>
+      </c>
+      <c r="B55" s="44" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="C55" s="44" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D55" s="44" t="inlineStr">
+        <is>
+          <t>Open Graph CMS-editable</t>
+        </is>
+      </c>
+      <c r="E55" s="44" t="inlineStr">
+        <is>
+          <t>Listing OK; detail OG image not wired</t>
+        </is>
+      </c>
+      <c r="F55" s="44" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="G55" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H55" s="44" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I55" s="44" t="inlineStr"/>
+      <c r="J55" s="44" t="inlineStr"/>
+      <c r="K55" s="44" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="44" t="inlineStr">
+        <is>
+          <t>BLOG-GAP-037</t>
+        </is>
+      </c>
+      <c r="B56" s="44" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="C56" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D56" s="44" t="inlineStr">
+        <is>
+          <t>Error/loading states, tests</t>
+        </is>
+      </c>
+      <c r="E56" s="44" t="inlineStr">
+        <is>
+          <t>No loading.tsx/error.tsx; no automated tests</t>
+        </is>
+      </c>
+      <c r="F56" s="44" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="G56" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H56" s="44" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I56" s="44" t="inlineStr"/>
+      <c r="J56" s="44" t="inlineStr"/>
+      <c r="K56" s="44" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A5:F5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M117"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" style="41" min="1" max="1"/>
+    <col width="14" customWidth="1" style="41" min="2" max="2"/>
+    <col width="28" customWidth="1" style="41" min="3" max="3"/>
+    <col width="32" customWidth="1" style="41" min="4" max="4"/>
+    <col width="40" customWidth="1" style="41" min="5" max="5"/>
+    <col width="50" customWidth="1" style="41" min="6" max="6"/>
+    <col width="10" customWidth="1" style="41" min="7" max="7"/>
+    <col width="14" customWidth="1" style="41" min="8" max="8"/>
+    <col width="22" customWidth="1" style="41" min="9" max="9"/>
+    <col width="22" customWidth="1" style="41" min="10" max="10"/>
+    <col width="10" customWidth="1" style="41" min="11" max="11"/>
+    <col width="30" customWidth="1" style="41" min="12" max="12"/>
+    <col width="30" customWidth="1" style="41" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="42" t="inlineStr">
+        <is>
+          <t>CONTACT US MODULE — TEST CASES</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Module:</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Contact Us</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Routes:</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>/contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Data Source:</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Strapi CMS (contact-page, generic-forms) + BFF /api/generic-submissions/submit</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PRD:</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>docs/prd/PRD-contact-us-page.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="42" t="inlineStr">
+        <is>
+          <t>GLOBAL PRECONDITIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B6" s="43" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Strapi CMS reachable with published contact-page single type</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PRE-02</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Generic form configured with matching formTag and reason dropdown options</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PRE-03</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Test on Desktop (&gt;=1280px), Tablet (~768px), Mobile (&lt;=390px)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PRE-04</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Browsers: Chrome, Safari, Firefox, Edge (latest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PRE-05</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Guest and logged-in Magento customer accounts available for prefill tests</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="42" t="inlineStr">
+        <is>
+          <t>TEST DATA RECOMMENDATIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="43" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="B14" s="43" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Valid enquiry</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Name: Jane Doe, Phone: 9876543210 (+91), Email: jane@example.com, Reason: Product enquiry, Message: 10+ chars</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Invalid phone +91</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Phone: 12345 (too short) or 5123456789 (invalid leading digit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Invalid email</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>test@, test@domain, missing@.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Long message</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>501+ character message to test max length validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Logged-in user</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Customer with name, email, phone in Magento profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CMS inactive hero</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>heroSection.isActive = false</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CMS inactive form</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>formSection.isActive = false</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="42" t="inlineStr">
+        <is>
+          <t>TEST CASES</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="43" t="inlineStr">
+        <is>
+          <t>TC ID</t>
+        </is>
+      </c>
+      <c r="B24" s="43" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="C24" s="43" t="inlineStr">
+        <is>
+          <t>Feature Area</t>
+        </is>
+      </c>
+      <c r="D24" s="43" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="E24" s="43" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="F24" s="43" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="G24" s="43" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="H24" s="43" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="I24" s="43" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="J24" s="43" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="K24" s="43" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="L24" s="43" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="M24" s="43" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-001</t>
+        </is>
+      </c>
+      <c r="B25" s="44" t="inlineStr">
+        <is>
+          <t>A. Page Load</t>
+        </is>
+      </c>
+      <c r="C25" s="44" t="inlineStr">
+        <is>
+          <t>Open Contact Us page</t>
+        </is>
+      </c>
+      <c r="D25" s="44" t="inlineStr">
+        <is>
+          <t>Navigate to /contact</t>
+        </is>
+      </c>
+      <c r="E25" s="44" t="inlineStr">
+        <is>
+          <t>Page loads with skeleton then CMS content; title 'Contact Us | Sunny Diamonds'</t>
+        </is>
+      </c>
+      <c r="F25" s="44" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G25" s="44" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H25" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I25" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J25" s="44" t="inlineStr"/>
+      <c r="K25" s="44" t="inlineStr"/>
+      <c r="L25" s="44" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-002</t>
+        </is>
+      </c>
+      <c r="B26" s="44" t="inlineStr">
+        <is>
+          <t>A. Page Load</t>
+        </is>
+      </c>
+      <c r="C26" s="44" t="inlineStr">
+        <is>
+          <t>ISR revalidation</t>
+        </is>
+      </c>
+      <c r="D26" s="44" t="inlineStr">
+        <is>
+          <t>Check page.tsx revalidate setting</t>
+        </is>
+      </c>
+      <c r="E26" s="44" t="inlineStr">
+        <is>
+          <t>revalidate = 300 (5 min ISR)</t>
+        </is>
+      </c>
+      <c r="F26" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G26" s="44" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="H26" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I26" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J26" s="44" t="inlineStr"/>
+      <c r="K26" s="44" t="inlineStr"/>
+      <c r="L26" s="44" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-003</t>
+        </is>
+      </c>
+      <c r="B27" s="44" t="inlineStr">
+        <is>
+          <t>A. Page Load</t>
+        </is>
+      </c>
+      <c r="C27" s="44" t="inlineStr">
+        <is>
+          <t>Sitemap inclusion</t>
+        </is>
+      </c>
+      <c r="D27" s="44" t="inlineStr">
+        <is>
+          <t>Open /sitemap.xml</t>
+        </is>
+      </c>
+      <c r="E27" s="44" t="inlineStr">
+        <is>
+          <t>/contact URL listed</t>
+        </is>
+      </c>
+      <c r="F27" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G27" s="44" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="H27" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I27" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J27" s="44" t="inlineStr"/>
+      <c r="K27" s="44" t="inlineStr"/>
+      <c r="L27" s="44" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-004</t>
+        </is>
+      </c>
+      <c r="B28" s="44" t="inlineStr">
+        <is>
+          <t>A. Page Load</t>
+        </is>
+      </c>
+      <c r="C28" s="44" t="inlineStr">
+        <is>
+          <t>Inbound navigation links</t>
+        </is>
+      </c>
+      <c r="D28" s="44" t="inlineStr">
+        <is>
+          <t>Click Contact Us from footer, profile orders, error page</t>
+        </is>
+      </c>
+      <c r="E28" s="44" t="inlineStr">
+        <is>
+          <t>All links route to /contact</t>
+        </is>
+      </c>
+      <c r="F28" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G28" s="44" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="H28" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I28" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J28" s="44" t="inlineStr"/>
+      <c r="K28" s="44" t="inlineStr"/>
+      <c r="L28" s="44" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-005</t>
+        </is>
+      </c>
+      <c r="B29" s="44" t="inlineStr">
+        <is>
+          <t>A. Page Load</t>
+        </is>
+      </c>
+      <c r="C29" s="44" t="inlineStr">
+        <is>
+          <t>CMS fetch failure</t>
+        </is>
+      </c>
+      <c r="D29" s="44" t="inlineStr">
+        <is>
+          <t>Simulate Strapi outage for contact-page</t>
+        </is>
+      </c>
+      <c r="E29" s="44" t="inlineStr">
+        <is>
+          <t>Page renders without sections; no crash; metadata uses site defaults</t>
+        </is>
+      </c>
+      <c r="F29" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G29" s="44" t="inlineStr">
+        <is>
+          <t>Resilience</t>
+        </is>
+      </c>
+      <c r="H29" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I29" s="44" t="inlineStr">
+        <is>
+          <t>CMS inactive</t>
+        </is>
+      </c>
+      <c r="J29" s="44" t="inlineStr">
+        <is>
+          <t>No user-facing error message</t>
+        </is>
+      </c>
+      <c r="K29" s="44" t="inlineStr"/>
+      <c r="L29" s="44" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-006</t>
+        </is>
+      </c>
+      <c r="B30" s="44" t="inlineStr">
+        <is>
+          <t>A. Page Load</t>
+        </is>
+      </c>
+      <c r="C30" s="44" t="inlineStr">
+        <is>
+          <t>All sections disabled in CMS</t>
+        </is>
+      </c>
+      <c r="D30" s="44" t="inlineStr">
+        <is>
+          <t>Disable hero, contact, form, visit in CMS</t>
+        </is>
+      </c>
+      <c r="E30" s="44" t="inlineStr">
+        <is>
+          <t>Minimal empty page without console errors</t>
+        </is>
+      </c>
+      <c r="F30" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G30" s="44" t="inlineStr">
+        <is>
+          <t>CMS</t>
+        </is>
+      </c>
+      <c r="H30" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I30" s="44" t="inlineStr">
+        <is>
+          <t>CMS inactive sections</t>
+        </is>
+      </c>
+      <c r="J30" s="44" t="inlineStr"/>
+      <c r="K30" s="44" t="inlineStr"/>
+      <c r="L30" s="44" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-007</t>
+        </is>
+      </c>
+      <c r="B31" s="44" t="inlineStr">
+        <is>
+          <t>A. Page Load</t>
+        </is>
+      </c>
+      <c r="C31" s="44" t="inlineStr">
+        <is>
+          <t>Loading skeleton</t>
+        </is>
+      </c>
+      <c r="D31" s="44" t="inlineStr">
+        <is>
+          <t>Hard refresh /contact on slow network</t>
+        </is>
+      </c>
+      <c r="E31" s="44" t="inlineStr">
+        <is>
+          <t>ContactPageSkeleton shown with aria-busy=true</t>
+        </is>
+      </c>
+      <c r="F31" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G31" s="44" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="H31" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I31" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J31" s="44" t="inlineStr"/>
+      <c r="K31" s="44" t="inlineStr"/>
+      <c r="L31" s="44" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-010</t>
+        </is>
+      </c>
+      <c r="B32" s="44" t="inlineStr">
+        <is>
+          <t>B. Hero</t>
+        </is>
+      </c>
+      <c r="C32" s="44" t="inlineStr">
+        <is>
+          <t>Hero renders from CMS</t>
+        </is>
+      </c>
+      <c r="D32" s="44" t="inlineStr">
+        <is>
+          <t>Open /contact with hero active</t>
+        </is>
+      </c>
+      <c r="E32" s="44" t="inlineStr">
+        <is>
+          <t>Hero h1 title visible; desktop/mobile image or video if configured</t>
+        </is>
+      </c>
+      <c r="F32" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G32" s="44" t="inlineStr">
+        <is>
+          <t>CMS</t>
+        </is>
+      </c>
+      <c r="H32" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I32" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J32" s="44" t="inlineStr"/>
+      <c r="K32" s="44" t="inlineStr"/>
+      <c r="L32" s="44" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-011</t>
+        </is>
+      </c>
+      <c r="B33" s="44" t="inlineStr">
+        <is>
+          <t>B. Hero</t>
+        </is>
+      </c>
+      <c r="C33" s="44" t="inlineStr">
+        <is>
+          <t>Hero hidden when inactive</t>
+        </is>
+      </c>
+      <c r="D33" s="44" t="inlineStr">
+        <is>
+          <t>Set heroSection.isActive=false in CMS</t>
+        </is>
+      </c>
+      <c r="E33" s="44" t="inlineStr">
+        <is>
+          <t>Hero section omitted; content shifts up</t>
+        </is>
+      </c>
+      <c r="F33" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G33" s="44" t="inlineStr">
+        <is>
+          <t>CMS</t>
+        </is>
+      </c>
+      <c r="H33" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I33" s="44" t="inlineStr">
+        <is>
+          <t>CMS inactive hero</t>
+        </is>
+      </c>
+      <c r="J33" s="44" t="inlineStr"/>
+      <c r="K33" s="44" t="inlineStr"/>
+      <c r="L33" s="44" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-012</t>
+        </is>
+      </c>
+      <c r="B34" s="44" t="inlineStr">
+        <is>
+          <t>B. Hero</t>
+        </is>
+      </c>
+      <c r="C34" s="44" t="inlineStr">
+        <is>
+          <t>Hero hidden without title</t>
+        </is>
+      </c>
+      <c r="D34" s="44" t="inlineStr">
+        <is>
+          <t>Remove hero title in CMS</t>
+        </is>
+      </c>
+      <c r="E34" s="44" t="inlineStr">
+        <is>
+          <t>Hero section not rendered</t>
+        </is>
+      </c>
+      <c r="F34" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G34" s="44" t="inlineStr">
+        <is>
+          <t>CMS</t>
+        </is>
+      </c>
+      <c r="H34" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I34" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J34" s="44" t="inlineStr"/>
+      <c r="K34" s="44" t="inlineStr"/>
+      <c r="L34" s="44" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-013</t>
+        </is>
+      </c>
+      <c r="B35" s="44" t="inlineStr">
+        <is>
+          <t>B. Hero</t>
+        </is>
+      </c>
+      <c r="C35" s="44" t="inlineStr">
+        <is>
+          <t>Hero LCP preload</t>
+        </is>
+      </c>
+      <c r="D35" s="44" t="inlineStr">
+        <is>
+          <t>Inspect network on page load</t>
+        </is>
+      </c>
+      <c r="E35" s="44" t="inlineStr">
+        <is>
+          <t>Hero images preloaded via preloadPlpHeroLcpImages</t>
+        </is>
+      </c>
+      <c r="F35" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G35" s="44" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="H35" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I35" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J35" s="44" t="inlineStr"/>
+      <c r="K35" s="44" t="inlineStr"/>
+      <c r="L35" s="44" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-020</t>
+        </is>
+      </c>
+      <c r="B36" s="44" t="inlineStr">
+        <is>
+          <t>C. Contact Cards</t>
+        </is>
+      </c>
+      <c r="C36" s="44" t="inlineStr">
+        <is>
+          <t>Intro text renders</t>
+        </is>
+      </c>
+      <c r="D36" s="44" t="inlineStr">
+        <is>
+          <t>View intro below hero</t>
+        </is>
+      </c>
+      <c r="E36" s="44" t="inlineStr">
+        <is>
+          <t>CMS introText displayed; mobile/desktop variants if different</t>
+        </is>
+      </c>
+      <c r="F36" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G36" s="44" t="inlineStr">
+        <is>
+          <t>CMS</t>
+        </is>
+      </c>
+      <c r="H36" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I36" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J36" s="44" t="inlineStr"/>
+      <c r="K36" s="44" t="inlineStr"/>
+      <c r="L36" s="44" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-021</t>
+        </is>
+      </c>
+      <c r="B37" s="44" t="inlineStr">
+        <is>
+          <t>C. Contact Cards</t>
+        </is>
+      </c>
+      <c r="C37" s="44" t="inlineStr">
+        <is>
+          <t>Call Us card</t>
+        </is>
+      </c>
+      <c r="D37" s="44" t="inlineStr">
+        <is>
+          <t>Verify Call Us card title, hours, phone link</t>
+        </is>
+      </c>
+      <c r="E37" s="44" t="inlineStr">
+        <is>
+          <t>Card shows phone number; hours parsed from Label: Value format</t>
+        </is>
+      </c>
+      <c r="F37" s="44" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G37" s="44" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H37" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I37" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J37" s="44" t="inlineStr"/>
+      <c r="K37" s="44" t="inlineStr"/>
+      <c r="L37" s="44" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-022</t>
+        </is>
+      </c>
+      <c r="B38" s="44" t="inlineStr">
+        <is>
+          <t>C. Contact Cards</t>
+        </is>
+      </c>
+      <c r="C38" s="44" t="inlineStr">
+        <is>
+          <t>Call Us desktop click</t>
+        </is>
+      </c>
+      <c r="D38" s="44" t="inlineStr">
+        <is>
+          <t>On desktop (&gt;=768px), click phone number</t>
+        </is>
+      </c>
+      <c r="E38" s="44" t="inlineStr">
+        <is>
+          <t>Number copied to clipboard; toast 'Phone number copied'; no dialer</t>
+        </is>
+      </c>
+      <c r="F38" s="44" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G38" s="44" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H38" s="44" t="inlineStr">
+        <is>
+          <t>PRE-03</t>
+        </is>
+      </c>
+      <c r="I38" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J38" s="44" t="inlineStr">
+        <is>
+          <t>Verified in browser</t>
+        </is>
+      </c>
+      <c r="K38" s="44" t="inlineStr"/>
+      <c r="L38" s="44" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-023</t>
+        </is>
+      </c>
+      <c r="B39" s="44" t="inlineStr">
+        <is>
+          <t>C. Contact Cards</t>
+        </is>
+      </c>
+      <c r="C39" s="44" t="inlineStr">
+        <is>
+          <t>Call Us mobile tap</t>
+        </is>
+      </c>
+      <c r="D39" s="44" t="inlineStr">
+        <is>
+          <t>On mobile (&lt;768px), tap phone number</t>
+        </is>
+      </c>
+      <c r="E39" s="44" t="inlineStr">
+        <is>
+          <t>Opens native dialer via tel: link</t>
+        </is>
+      </c>
+      <c r="F39" s="44" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G39" s="44" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H39" s="44" t="inlineStr">
+        <is>
+          <t>PRE-03</t>
+        </is>
+      </c>
+      <c r="I39" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J39" s="44" t="inlineStr"/>
+      <c r="K39" s="44" t="inlineStr"/>
+      <c r="L39" s="44" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-024</t>
+        </is>
+      </c>
+      <c r="B40" s="44" t="inlineStr">
+        <is>
+          <t>C. Contact Cards</t>
+        </is>
+      </c>
+      <c r="C40" s="44" t="inlineStr">
+        <is>
+          <t>Viewport resize phone behavior</t>
+        </is>
+      </c>
+      <c r="D40" s="44" t="inlineStr">
+        <is>
+          <t>Resize 767px ↔ 768px and interact with phone</t>
+        </is>
+      </c>
+      <c r="E40" s="44" t="inlineStr">
+        <is>
+          <t>Behavior switches between copy and dial on re-render</t>
+        </is>
+      </c>
+      <c r="F40" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G40" s="44" t="inlineStr">
+        <is>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="H40" s="44" t="inlineStr">
+        <is>
+          <t>PRE-03</t>
+        </is>
+      </c>
+      <c r="I40" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J40" s="44" t="inlineStr"/>
+      <c r="K40" s="44" t="inlineStr"/>
+      <c r="L40" s="44" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-025</t>
+        </is>
+      </c>
+      <c r="B41" s="44" t="inlineStr">
+        <is>
+          <t>C. Contact Cards</t>
+        </is>
+      </c>
+      <c r="C41" s="44" t="inlineStr">
+        <is>
+          <t>Clipboard denied</t>
+        </is>
+      </c>
+      <c r="D41" s="44" t="inlineStr">
+        <is>
+          <t>Block clipboard permission; click phone on desktop</t>
+        </is>
+      </c>
+      <c r="E41" s="44" t="inlineStr">
+        <is>
+          <t>Toast 'Unable to copy' with manual copy guidance</t>
+        </is>
+      </c>
+      <c r="F41" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G41" s="44" t="inlineStr">
+        <is>
+          <t>Edge Case</t>
+        </is>
+      </c>
+      <c r="H41" s="44" t="inlineStr">
+        <is>
+          <t>PRE-03</t>
+        </is>
+      </c>
+      <c r="I41" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J41" s="44" t="inlineStr"/>
+      <c r="K41" s="44" t="inlineStr"/>
+      <c r="L41" s="44" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-026</t>
+        </is>
+      </c>
+      <c r="B42" s="44" t="inlineStr">
+        <is>
+          <t>C. Contact Cards</t>
+        </is>
+      </c>
+      <c r="C42" s="44" t="inlineStr">
+        <is>
+          <t>Email card mailto</t>
+        </is>
+      </c>
+      <c r="D42" s="44" t="inlineStr">
+        <is>
+          <t>Click email CTA</t>
+        </is>
+      </c>
+      <c r="E42" s="44" t="inlineStr">
+        <is>
+          <t>Opens mail client with mailto: link</t>
+        </is>
+      </c>
+      <c r="F42" s="44" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G42" s="44" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H42" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I42" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J42" s="44" t="inlineStr"/>
+      <c r="K42" s="44" t="inlineStr"/>
+      <c r="L42" s="44" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-027</t>
+        </is>
+      </c>
+      <c r="B43" s="44" t="inlineStr">
+        <is>
+          <t>C. Contact Cards</t>
+        </is>
+      </c>
+      <c r="C43" s="44" t="inlineStr">
+        <is>
+          <t>WhatsApp card</t>
+        </is>
+      </c>
+      <c r="D43" s="44" t="inlineStr">
+        <is>
+          <t>Click WhatsApp CTA</t>
+        </is>
+      </c>
+      <c r="E43" s="44" t="inlineStr">
+        <is>
+          <t>Opens wa.me or external WhatsApp URL in new tab</t>
+        </is>
+      </c>
+      <c r="F43" s="44" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G43" s="44" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H43" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I43" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J43" s="44" t="inlineStr"/>
+      <c r="K43" s="44" t="inlineStr"/>
+      <c r="L43" s="44" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-028</t>
+        </is>
+      </c>
+      <c r="B44" s="44" t="inlineStr">
+        <is>
+          <t>C. Contact Cards</t>
+        </is>
+      </c>
+      <c r="C44" s="44" t="inlineStr">
+        <is>
+          <t>Card grid layout desktop</t>
+        </is>
+      </c>
+      <c r="D44" s="44" t="inlineStr">
+        <is>
+          <t>View cards at &gt;=768px</t>
+        </is>
+      </c>
+      <c r="E44" s="44" t="inlineStr">
+        <is>
+          <t>3-column grid; cards equal height</t>
+        </is>
+      </c>
+      <c r="F44" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G44" s="44" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="H44" s="44" t="inlineStr">
+        <is>
+          <t>PRE-03</t>
+        </is>
+      </c>
+      <c r="I44" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J44" s="44" t="inlineStr"/>
+      <c r="K44" s="44" t="inlineStr"/>
+      <c r="L44" s="44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-029</t>
+        </is>
+      </c>
+      <c r="B45" s="44" t="inlineStr">
+        <is>
+          <t>C. Contact Cards</t>
+        </is>
+      </c>
+      <c r="C45" s="44" t="inlineStr">
+        <is>
+          <t>Card stack layout mobile</t>
+        </is>
+      </c>
+      <c r="D45" s="44" t="inlineStr">
+        <is>
+          <t>View cards at &lt;768px</t>
+        </is>
+      </c>
+      <c r="E45" s="44" t="inlineStr">
+        <is>
+          <t>Stacked cards with dividers and icons</t>
+        </is>
+      </c>
+      <c r="F45" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G45" s="44" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="H45" s="44" t="inlineStr">
+        <is>
+          <t>PRE-03</t>
+        </is>
+      </c>
+      <c r="I45" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J45" s="44" t="inlineStr"/>
+      <c r="K45" s="44" t="inlineStr"/>
+      <c r="L45" s="44" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-030</t>
+        </is>
+      </c>
+      <c r="B46" s="44" t="inlineStr">
+        <is>
+          <t>C. Contact Cards</t>
+        </is>
+      </c>
+      <c r="C46" s="44" t="inlineStr">
+        <is>
+          <t>Inactive card omitted</t>
+        </is>
+      </c>
+      <c r="D46" s="44" t="inlineStr">
+        <is>
+          <t>Set contactOption.isActive=false for one card</t>
+        </is>
+      </c>
+      <c r="E46" s="44" t="inlineStr">
+        <is>
+          <t>Card not shown; remaining cards render</t>
+        </is>
+      </c>
+      <c r="F46" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G46" s="44" t="inlineStr">
+        <is>
+          <t>CMS</t>
+        </is>
+      </c>
+      <c r="H46" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I46" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J46" s="44" t="inlineStr"/>
+      <c r="K46" s="44" t="inlineStr"/>
+      <c r="L46" s="44" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-031</t>
+        </is>
+      </c>
+      <c r="B47" s="44" t="inlineStr">
+        <is>
+          <t>C. Contact Cards</t>
+        </is>
+      </c>
+      <c r="C47" s="44" t="inlineStr">
+        <is>
+          <t>Card without actionable value</t>
+        </is>
+      </c>
+      <c r="D47" s="44" t="inlineStr">
+        <is>
+          <t>Card with empty/invalid value</t>
+        </is>
+      </c>
+      <c r="E47" s="44" t="inlineStr">
+        <is>
+          <t>Card skipped by mapper</t>
+        </is>
+      </c>
+      <c r="F47" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G47" s="44" t="inlineStr">
+        <is>
+          <t>CMS</t>
+        </is>
+      </c>
+      <c r="H47" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I47" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J47" s="44" t="inlineStr"/>
+      <c r="K47" s="44" t="inlineStr"/>
+      <c r="L47" s="44" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-032</t>
+        </is>
+      </c>
+      <c r="B48" s="44" t="inlineStr">
+        <is>
+          <t>C. Contact Cards</t>
+        </is>
+      </c>
+      <c r="C48" s="44" t="inlineStr">
+        <is>
+          <t>Mobile title variant</t>
+        </is>
+      </c>
+      <c r="D48" s="44" t="inlineStr">
+        <is>
+          <t>Check email card on mobile</t>
+        </is>
+      </c>
+      <c r="E48" s="44" t="inlineStr">
+        <is>
+          <t>Uses card.title (mobileTitle from mapper not applied)</t>
+        </is>
+      </c>
+      <c r="F48" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G48" s="44" t="inlineStr">
+        <is>
+          <t>UI Gap</t>
+        </is>
+      </c>
+      <c r="H48" s="44" t="inlineStr">
+        <is>
+          <t>PRE-03</t>
+        </is>
+      </c>
+      <c r="I48" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J48" s="44" t="inlineStr">
+        <is>
+          <t>ISSUE: mobileTitle unused</t>
+        </is>
+      </c>
+      <c r="K48" s="44" t="inlineStr"/>
+      <c r="L48" s="44" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-040</t>
+        </is>
+      </c>
+      <c r="B49" s="44" t="inlineStr">
+        <is>
+          <t>D. Form UI</t>
+        </is>
+      </c>
+      <c r="C49" s="44" t="inlineStr">
+        <is>
+          <t>Form section renders</t>
+        </is>
+      </c>
+      <c r="D49" s="44" t="inlineStr">
+        <is>
+          <t>Scroll to enquiry form</t>
+        </is>
+      </c>
+      <c r="E49" s="44" t="inlineStr">
+        <is>
+          <t>Form title, all fields, consent, submit button visible</t>
+        </is>
+      </c>
+      <c r="F49" s="44" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G49" s="44" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H49" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01, PRE-02</t>
+        </is>
+      </c>
+      <c r="I49" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J49" s="44" t="inlineStr"/>
+      <c r="K49" s="44" t="inlineStr"/>
+      <c r="L49" s="44" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-041</t>
+        </is>
+      </c>
+      <c r="B50" s="44" t="inlineStr">
+        <is>
+          <t>D. Form UI</t>
+        </is>
+      </c>
+      <c r="C50" s="44" t="inlineStr">
+        <is>
+          <t>Form hidden when inactive</t>
+        </is>
+      </c>
+      <c r="D50" s="44" t="inlineStr">
+        <is>
+          <t>Disable formSection in CMS</t>
+        </is>
+      </c>
+      <c r="E50" s="44" t="inlineStr">
+        <is>
+          <t>Form section not rendered</t>
+        </is>
+      </c>
+      <c r="F50" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G50" s="44" t="inlineStr">
+        <is>
+          <t>CMS</t>
+        </is>
+      </c>
+      <c r="H50" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I50" s="44" t="inlineStr">
+        <is>
+          <t>CMS inactive form</t>
+        </is>
+      </c>
+      <c r="J50" s="44" t="inlineStr"/>
+      <c r="K50" s="44" t="inlineStr"/>
+      <c r="L50" s="44" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-042</t>
+        </is>
+      </c>
+      <c r="B51" s="44" t="inlineStr">
+        <is>
+          <t>D. Form UI</t>
+        </is>
+      </c>
+      <c r="C51" s="44" t="inlineStr">
+        <is>
+          <t>Form hidden without formTag</t>
+        </is>
+      </c>
+      <c r="D51" s="44" t="inlineStr">
+        <is>
+          <t>Remove formTag from CMS</t>
+        </is>
+      </c>
+      <c r="E51" s="44" t="inlineStr">
+        <is>
+          <t>Form section omitted</t>
+        </is>
+      </c>
+      <c r="F51" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G51" s="44" t="inlineStr">
+        <is>
+          <t>CMS</t>
+        </is>
+      </c>
+      <c r="H51" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I51" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J51" s="44" t="inlineStr"/>
+      <c r="K51" s="44" t="inlineStr"/>
+      <c r="L51" s="44" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-043</t>
+        </is>
+      </c>
+      <c r="B52" s="44" t="inlineStr">
+        <is>
+          <t>D. Form UI</t>
+        </is>
+      </c>
+      <c r="C52" s="44" t="inlineStr">
+        <is>
+          <t>Field labels from CMS</t>
+        </is>
+      </c>
+      <c r="D52" s="44" t="inlineStr">
+        <is>
+          <t>Inspect form labels</t>
+        </is>
+      </c>
+      <c r="E52" s="44" t="inlineStr">
+        <is>
+          <t>Name, Phone, Email, Reason, Message labels match CMS dynamicFields</t>
+        </is>
+      </c>
+      <c r="F52" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G52" s="44" t="inlineStr">
+        <is>
+          <t>CMS</t>
+        </is>
+      </c>
+      <c r="H52" s="44" t="inlineStr">
+        <is>
+          <t>PRE-02</t>
+        </is>
+      </c>
+      <c r="I52" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J52" s="44" t="inlineStr"/>
+      <c r="K52" s="44" t="inlineStr"/>
+      <c r="L52" s="44" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-044</t>
+        </is>
+      </c>
+      <c r="B53" s="44" t="inlineStr">
+        <is>
+          <t>D. Form UI</t>
+        </is>
+      </c>
+      <c r="C53" s="44" t="inlineStr">
+        <is>
+          <t>Phone country code select</t>
+        </is>
+      </c>
+      <c r="D53" s="44" t="inlineStr">
+        <is>
+          <t>Open country code dropdown</t>
+        </is>
+      </c>
+      <c r="E53" s="44" t="inlineStr">
+        <is>
+          <t>Options: +91, +1, +44; aria-label='Country code'</t>
+        </is>
+      </c>
+      <c r="F53" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G53" s="44" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H53" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I53" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J53" s="44" t="inlineStr"/>
+      <c r="K53" s="44" t="inlineStr"/>
+      <c r="L53" s="44" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-045</t>
+        </is>
+      </c>
+      <c r="B54" s="44" t="inlineStr">
+        <is>
+          <t>D. Form UI</t>
+        </is>
+      </c>
+      <c r="C54" s="44" t="inlineStr">
+        <is>
+          <t>Reason dropdown options</t>
+        </is>
+      </c>
+      <c r="D54" s="44" t="inlineStr">
+        <is>
+          <t>Open reason dropdown</t>
+        </is>
+      </c>
+      <c r="E54" s="44" t="inlineStr">
+        <is>
+          <t>CMS options shown (e.g. Product enquiry, Order Support, Other)</t>
+        </is>
+      </c>
+      <c r="F54" s="44" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G54" s="44" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H54" s="44" t="inlineStr">
+        <is>
+          <t>PRE-02</t>
+        </is>
+      </c>
+      <c r="I54" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J54" s="44" t="inlineStr">
+        <is>
+          <t>Verified: 6 options in browser</t>
+        </is>
+      </c>
+      <c r="K54" s="44" t="inlineStr"/>
+      <c r="L54" s="44" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-046</t>
+        </is>
+      </c>
+      <c r="B55" s="44" t="inlineStr">
+        <is>
+          <t>D. Form UI</t>
+        </is>
+      </c>
+      <c r="C55" s="44" t="inlineStr">
+        <is>
+          <t>Field placeholders</t>
+        </is>
+      </c>
+      <c r="D55" s="44" t="inlineStr">
+        <is>
+          <t>Inspect phone and email placeholders</t>
+        </is>
+      </c>
+      <c r="E55" s="44" t="inlineStr">
+        <is>
+          <t>Field-specific placeholders from CMS</t>
+        </is>
+      </c>
+      <c r="F55" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G55" s="44" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="H55" s="44" t="inlineStr">
+        <is>
+          <t>PRE-02</t>
+        </is>
+      </c>
+      <c r="I55" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J55" s="44" t="inlineStr">
+        <is>
+          <t>FAIL: both show 'Full Name'</t>
+        </is>
+      </c>
+      <c r="K55" s="44" t="inlineStr"/>
+      <c r="L55" s="44" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-047</t>
+        </is>
+      </c>
+      <c r="B56" s="44" t="inlineStr">
+        <is>
+          <t>D. Form UI</t>
+        </is>
+      </c>
+      <c r="C56" s="44" t="inlineStr">
+        <is>
+          <t>Message placeholder</t>
+        </is>
+      </c>
+      <c r="D56" s="44" t="inlineStr">
+        <is>
+          <t>Inspect message textarea placeholder</t>
+        </is>
+      </c>
+      <c r="E56" s="44" t="inlineStr">
+        <is>
+          <t>CMS message placeholder shown</t>
+        </is>
+      </c>
+      <c r="F56" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G56" s="44" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="H56" s="44" t="inlineStr">
+        <is>
+          <t>PRE-02</t>
+        </is>
+      </c>
+      <c r="I56" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J56" s="44" t="inlineStr"/>
+      <c r="K56" s="44" t="inlineStr"/>
+      <c r="L56" s="44" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-048</t>
+        </is>
+      </c>
+      <c r="B57" s="44" t="inlineStr">
+        <is>
+          <t>D. Form UI</t>
+        </is>
+      </c>
+      <c r="C57" s="44" t="inlineStr">
+        <is>
+          <t>Desktop 2-column phone/email</t>
+        </is>
+      </c>
+      <c r="D57" s="44" t="inlineStr">
+        <is>
+          <t>View form at &gt;=768px</t>
+        </is>
+      </c>
+      <c r="E57" s="44" t="inlineStr">
+        <is>
+          <t>Phone and email fields side by side</t>
+        </is>
+      </c>
+      <c r="F57" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G57" s="44" t="inlineStr">
+        <is>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="H57" s="44" t="inlineStr">
+        <is>
+          <t>PRE-03</t>
+        </is>
+      </c>
+      <c r="I57" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J57" s="44" t="inlineStr"/>
+      <c r="K57" s="44" t="inlineStr"/>
+      <c r="L57" s="44" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-049</t>
+        </is>
+      </c>
+      <c r="B58" s="44" t="inlineStr">
+        <is>
+          <t>D. Form UI</t>
+        </is>
+      </c>
+      <c r="C58" s="44" t="inlineStr">
+        <is>
+          <t>Submit button full width mobile</t>
+        </is>
+      </c>
+      <c r="D58" s="44" t="inlineStr">
+        <is>
+          <t>View submit at &lt;768px</t>
+        </is>
+      </c>
+      <c r="E58" s="44" t="inlineStr">
+        <is>
+          <t>Submit button spans full width</t>
+        </is>
+      </c>
+      <c r="F58" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G58" s="44" t="inlineStr">
+        <is>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="H58" s="44" t="inlineStr">
+        <is>
+          <t>PRE-03</t>
+        </is>
+      </c>
+      <c r="I58" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J58" s="44" t="inlineStr"/>
+      <c r="K58" s="44" t="inlineStr"/>
+      <c r="L58" s="44" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-050</t>
+        </is>
+      </c>
+      <c r="B59" s="44" t="inlineStr">
+        <is>
+          <t>D. Form UI</t>
+        </is>
+      </c>
+      <c r="C59" s="44" t="inlineStr">
+        <is>
+          <t>Live form config refresh</t>
+        </is>
+      </c>
+      <c r="D59" s="44" t="inlineStr">
+        <is>
+          <t>Update generic-forms reason options in CMS</t>
+        </is>
+      </c>
+      <c r="E59" s="44" t="inlineStr">
+        <is>
+          <t>Client fetches updated options without republishing contact page</t>
+        </is>
+      </c>
+      <c r="F59" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G59" s="44" t="inlineStr">
+        <is>
+          <t>CMS</t>
+        </is>
+      </c>
+      <c r="H59" s="44" t="inlineStr">
+        <is>
+          <t>PRE-02</t>
+        </is>
+      </c>
+      <c r="I59" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J59" s="44" t="inlineStr"/>
+      <c r="K59" s="44" t="inlineStr"/>
+      <c r="L59" s="44" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-060</t>
+        </is>
+      </c>
+      <c r="B60" s="44" t="inlineStr">
+        <is>
+          <t>E. Validation</t>
+        </is>
+      </c>
+      <c r="C60" s="44" t="inlineStr">
+        <is>
+          <t>Submit empty form</t>
+        </is>
+      </c>
+      <c r="D60" s="44" t="inlineStr">
+        <is>
+          <t>Click Submit with all fields empty</t>
+        </is>
+      </c>
+      <c r="E60" s="44" t="inlineStr">
+        <is>
+          <t>Inline validation errors on all required fields</t>
+        </is>
+      </c>
+      <c r="F60" s="44" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G60" s="44" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="H60" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I60" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J60" s="44" t="inlineStr">
+        <is>
+          <t>FAIL: Submit disabled</t>
+        </is>
+      </c>
+      <c r="K60" s="44" t="inlineStr"/>
+      <c r="L60" s="44" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-061</t>
+        </is>
+      </c>
+      <c r="B61" s="44" t="inlineStr">
+        <is>
+          <t>E. Validation</t>
+        </is>
+      </c>
+      <c r="C61" s="44" t="inlineStr">
+        <is>
+          <t>Name required</t>
+        </is>
+      </c>
+      <c r="D61" s="44" t="inlineStr">
+        <is>
+          <t>Leave name empty; blur field</t>
+        </is>
+      </c>
+      <c r="E61" s="44" t="inlineStr">
+        <is>
+          <t>Error shown after blur</t>
+        </is>
+      </c>
+      <c r="F61" s="44" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G61" s="44" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="H61" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I61" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J61" s="44" t="inlineStr"/>
+      <c r="K61" s="44" t="inlineStr"/>
+      <c r="L61" s="44" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-062</t>
+        </is>
+      </c>
+      <c r="B62" s="44" t="inlineStr">
+        <is>
+          <t>E. Validation</t>
+        </is>
+      </c>
+      <c r="C62" s="44" t="inlineStr">
+        <is>
+          <t>Name min length</t>
+        </is>
+      </c>
+      <c r="D62" s="44" t="inlineStr">
+        <is>
+          <t>Enter 1 char name; submit</t>
+        </is>
+      </c>
+      <c r="E62" s="44" t="inlineStr">
+        <is>
+          <t>Error: min 2 characters</t>
+        </is>
+      </c>
+      <c r="F62" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G62" s="44" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="H62" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I62" s="44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J62" s="44" t="inlineStr"/>
+      <c r="K62" s="44" t="inlineStr"/>
+      <c r="L62" s="44" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-063</t>
+        </is>
+      </c>
+      <c r="B63" s="44" t="inlineStr">
+        <is>
+          <t>E. Validation</t>
+        </is>
+      </c>
+      <c r="C63" s="44" t="inlineStr">
+        <is>
+          <t>Name max length</t>
+        </is>
+      </c>
+      <c r="D63" s="44" t="inlineStr">
+        <is>
+          <t>Enter 81+ char name</t>
+        </is>
+      </c>
+      <c r="E63" s="44" t="inlineStr">
+        <is>
+          <t>Error or input limited to 80 chars</t>
+        </is>
+      </c>
+      <c r="F63" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G63" s="44" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="H63" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I63" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J63" s="44" t="inlineStr"/>
+      <c r="K63" s="44" t="inlineStr"/>
+      <c r="L63" s="44" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-064</t>
+        </is>
+      </c>
+      <c r="B64" s="44" t="inlineStr">
+        <is>
+          <t>E. Validation</t>
+        </is>
+      </c>
+      <c r="C64" s="44" t="inlineStr">
+        <is>
+          <t>Name invalid chars</t>
+        </is>
+      </c>
+      <c r="D64" s="44" t="inlineStr">
+        <is>
+          <t>Enter name with numbers/symbols</t>
+        </is>
+      </c>
+      <c r="E64" s="44" t="inlineStr">
+        <is>
+          <t>Validation error for invalid characters</t>
+        </is>
+      </c>
+      <c r="F64" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G64" s="44" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="H64" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I64" s="44" t="inlineStr">
+        <is>
+          <t>John@123</t>
+        </is>
+      </c>
+      <c r="J64" s="44" t="inlineStr"/>
+      <c r="K64" s="44" t="inlineStr"/>
+      <c r="L64" s="44" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-065</t>
+        </is>
+      </c>
+      <c r="B65" s="44" t="inlineStr">
+        <is>
+          <t>E. Validation</t>
+        </is>
+      </c>
+      <c r="C65" s="44" t="inlineStr">
+        <is>
+          <t>Phone required +91</t>
+        </is>
+      </c>
+      <c r="D65" s="44" t="inlineStr">
+        <is>
+          <t>Leave phone empty; blur</t>
+        </is>
+      </c>
+      <c r="E65" s="44" t="inlineStr">
+        <is>
+          <t>Phone required error</t>
+        </is>
+      </c>
+      <c r="F65" s="44" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G65" s="44" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="H65" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I65" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J65" s="44" t="inlineStr"/>
+      <c r="K65" s="44" t="inlineStr"/>
+      <c r="L65" s="44" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-066</t>
+        </is>
+      </c>
+      <c r="B66" s="44" t="inlineStr">
+        <is>
+          <t>E. Validation</t>
+        </is>
+      </c>
+      <c r="C66" s="44" t="inlineStr">
+        <is>
+          <t>Phone +91 format</t>
+        </is>
+      </c>
+      <c r="D66" s="44" t="inlineStr">
+        <is>
+          <t>Enter invalid +91 numbers</t>
+        </is>
+      </c>
+      <c r="E66" s="44" t="inlineStr">
+        <is>
+          <t>Must be 10 digits starting 6-9</t>
+        </is>
+      </c>
+      <c r="F66" s="44" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G66" s="44" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="H66" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I66" s="44" t="inlineStr">
+        <is>
+          <t>Invalid phone +91</t>
+        </is>
+      </c>
+      <c r="J66" s="44" t="inlineStr"/>
+      <c r="K66" s="44" t="inlineStr"/>
+      <c r="L66" s="44" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-067</t>
+        </is>
+      </c>
+      <c r="B67" s="44" t="inlineStr">
+        <is>
+          <t>E. Validation</t>
+        </is>
+      </c>
+      <c r="C67" s="44" t="inlineStr">
+        <is>
+          <t>Phone +1 format</t>
+        </is>
+      </c>
+      <c r="D67" s="44" t="inlineStr">
+        <is>
+          <t>Switch to +1; enter invalid length</t>
+        </is>
+      </c>
+      <c r="E67" s="44" t="inlineStr">
+        <is>
+          <t>Exactly 10 digits required</t>
+        </is>
+      </c>
+      <c r="F67" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G67" s="44" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="H67" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I67" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J67" s="44" t="inlineStr"/>
+      <c r="K67" s="44" t="inlineStr"/>
+      <c r="L67" s="44" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-068</t>
+        </is>
+      </c>
+      <c r="B68" s="44" t="inlineStr">
+        <is>
+          <t>E. Validation</t>
+        </is>
+      </c>
+      <c r="C68" s="44" t="inlineStr">
+        <is>
+          <t>Phone +44 format</t>
+        </is>
+      </c>
+      <c r="D68" s="44" t="inlineStr">
+        <is>
+          <t>Switch to +44; enter 9 digits</t>
+        </is>
+      </c>
+      <c r="E68" s="44" t="inlineStr">
+        <is>
+          <t>10-11 digits required</t>
+        </is>
+      </c>
+      <c r="F68" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G68" s="44" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="H68" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I68" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J68" s="44" t="inlineStr"/>
+      <c r="K68" s="44" t="inlineStr"/>
+      <c r="L68" s="44" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-069</t>
+        </is>
+      </c>
+      <c r="B69" s="44" t="inlineStr">
+        <is>
+          <t>E. Validation</t>
+        </is>
+      </c>
+      <c r="C69" s="44" t="inlineStr">
+        <is>
+          <t>Phone digit sanitization</t>
+        </is>
+      </c>
+      <c r="D69" s="44" t="inlineStr">
+        <is>
+          <t>Type letters in phone field</t>
+        </is>
+      </c>
+      <c r="E69" s="44" t="inlineStr">
+        <is>
+          <t>Only digits accepted; max length enforced per country</t>
+        </is>
+      </c>
+      <c r="F69" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G69" s="44" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="H69" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I69" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J69" s="44" t="inlineStr"/>
+      <c r="K69" s="44" t="inlineStr"/>
+      <c r="L69" s="44" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-070</t>
+        </is>
+      </c>
+      <c r="B70" s="44" t="inlineStr">
+        <is>
+          <t>E. Validation</t>
+        </is>
+      </c>
+      <c r="C70" s="44" t="inlineStr">
+        <is>
+          <t>Email required</t>
+        </is>
+      </c>
+      <c r="D70" s="44" t="inlineStr">
+        <is>
+          <t>Leave email empty; blur</t>
+        </is>
+      </c>
+      <c r="E70" s="44" t="inlineStr">
+        <is>
+          <t>Email required error</t>
+        </is>
+      </c>
+      <c r="F70" s="44" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G70" s="44" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="H70" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I70" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J70" s="44" t="inlineStr"/>
+      <c r="K70" s="44" t="inlineStr"/>
+      <c r="L70" s="44" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-071</t>
+        </is>
+      </c>
+      <c r="B71" s="44" t="inlineStr">
+        <is>
+          <t>E. Validation</t>
+        </is>
+      </c>
+      <c r="C71" s="44" t="inlineStr">
+        <is>
+          <t>Email format</t>
+        </is>
+      </c>
+      <c r="D71" s="44" t="inlineStr">
+        <is>
+          <t>Enter malformed emails</t>
+        </is>
+      </c>
+      <c r="E71" s="44" t="inlineStr">
+        <is>
+          <t>Invalid email error</t>
+        </is>
+      </c>
+      <c r="F71" s="44" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G71" s="44" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="H71" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I71" s="44" t="inlineStr">
+        <is>
+          <t>Invalid email</t>
+        </is>
+      </c>
+      <c r="J71" s="44" t="inlineStr"/>
+      <c r="K71" s="44" t="inlineStr"/>
+      <c r="L71" s="44" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-072</t>
+        </is>
+      </c>
+      <c r="B72" s="44" t="inlineStr">
+        <is>
+          <t>E. Validation</t>
+        </is>
+      </c>
+      <c r="C72" s="44" t="inlineStr">
+        <is>
+          <t>Reason required</t>
+        </is>
+      </c>
+      <c r="D72" s="44" t="inlineStr">
+        <is>
+          <t>Fill all fields except reason; enable submit; submit</t>
+        </is>
+      </c>
+      <c r="E72" s="44" t="inlineStr">
+        <is>
+          <t>Error: Please select a reason</t>
+        </is>
+      </c>
+      <c r="F72" s="44" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G72" s="44" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="H72" s="44" t="inlineStr">
+        <is>
+          <t>PRE-02</t>
+        </is>
+      </c>
+      <c r="I72" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J72" s="44" t="inlineStr"/>
+      <c r="K72" s="44" t="inlineStr"/>
+      <c r="L72" s="44" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-073</t>
+        </is>
+      </c>
+      <c r="B73" s="44" t="inlineStr">
+        <is>
+          <t>E. Validation</t>
+        </is>
+      </c>
+      <c r="C73" s="44" t="inlineStr">
+        <is>
+          <t>Message required</t>
+        </is>
+      </c>
+      <c r="D73" s="44" t="inlineStr">
+        <is>
+          <t>Leave message empty; submit</t>
+        </is>
+      </c>
+      <c r="E73" s="44" t="inlineStr">
+        <is>
+          <t>Message required error</t>
+        </is>
+      </c>
+      <c r="F73" s="44" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G73" s="44" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="H73" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I73" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J73" s="44" t="inlineStr"/>
+      <c r="K73" s="44" t="inlineStr"/>
+      <c r="L73" s="44" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-074</t>
+        </is>
+      </c>
+      <c r="B74" s="44" t="inlineStr">
+        <is>
+          <t>E. Validation</t>
+        </is>
+      </c>
+      <c r="C74" s="44" t="inlineStr">
+        <is>
+          <t>Message min length</t>
+        </is>
+      </c>
+      <c r="D74" s="44" t="inlineStr">
+        <is>
+          <t>Enter &lt;10 char message</t>
+        </is>
+      </c>
+      <c r="E74" s="44" t="inlineStr">
+        <is>
+          <t>Min 10 characters error</t>
+        </is>
+      </c>
+      <c r="F74" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G74" s="44" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="H74" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I74" s="44" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="J74" s="44" t="inlineStr"/>
+      <c r="K74" s="44" t="inlineStr"/>
+      <c r="L74" s="44" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-075</t>
+        </is>
+      </c>
+      <c r="B75" s="44" t="inlineStr">
+        <is>
+          <t>E. Validation</t>
+        </is>
+      </c>
+      <c r="C75" s="44" t="inlineStr">
+        <is>
+          <t>Message max length</t>
+        </is>
+      </c>
+      <c r="D75" s="44" t="inlineStr">
+        <is>
+          <t>Enter 501+ char message and submit</t>
+        </is>
+      </c>
+      <c r="E75" s="44" t="inlineStr">
+        <is>
+          <t>Max 500 characters error</t>
+        </is>
+      </c>
+      <c r="F75" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G75" s="44" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="H75" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I75" s="44" t="inlineStr">
+        <is>
+          <t>Long message</t>
+        </is>
+      </c>
+      <c r="J75" s="44" t="inlineStr">
+        <is>
+          <t>No maxlength on textarea</t>
+        </is>
+      </c>
+      <c r="K75" s="44" t="inlineStr"/>
+      <c r="L75" s="44" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-076</t>
+        </is>
+      </c>
+      <c r="B76" s="44" t="inlineStr">
+        <is>
+          <t>E. Validation</t>
+        </is>
+      </c>
+      <c r="C76" s="44" t="inlineStr">
+        <is>
+          <t>Consent required</t>
+        </is>
+      </c>
+      <c r="D76" s="44" t="inlineStr">
+        <is>
+          <t>Fill form but leave consent unchecked; submit</t>
+        </is>
+      </c>
+      <c r="E76" s="44" t="inlineStr">
+        <is>
+          <t>Error: Please accept the terms to continue</t>
+        </is>
+      </c>
+      <c r="F76" s="44" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G76" s="44" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="H76" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I76" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J76" s="44" t="inlineStr"/>
+      <c r="K76" s="44" t="inlineStr"/>
+      <c r="L76" s="44" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-077</t>
+        </is>
+      </c>
+      <c r="B77" s="44" t="inlineStr">
+        <is>
+          <t>E. Validation</t>
+        </is>
+      </c>
+      <c r="C77" s="44" t="inlineStr">
+        <is>
+          <t>Errors on blur</t>
+        </is>
+      </c>
+      <c r="D77" s="44" t="inlineStr">
+        <is>
+          <t>Tab through fields leaving invalid values</t>
+        </is>
+      </c>
+      <c r="E77" s="44" t="inlineStr">
+        <is>
+          <t>Errors appear per field on blur before submit</t>
+        </is>
+      </c>
+      <c r="F77" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G77" s="44" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="H77" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I77" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J77" s="44" t="inlineStr"/>
+      <c r="K77" s="44" t="inlineStr"/>
+      <c r="L77" s="44" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-078</t>
+        </is>
+      </c>
+      <c r="B78" s="44" t="inlineStr">
+        <is>
+          <t>E. Validation</t>
+        </is>
+      </c>
+      <c r="C78" s="44" t="inlineStr">
+        <is>
+          <t>aria-invalid on errors</t>
+        </is>
+      </c>
+      <c r="D78" s="44" t="inlineStr">
+        <is>
+          <t>Trigger field error</t>
+        </is>
+      </c>
+      <c r="E78" s="44" t="inlineStr">
+        <is>
+          <t>aria-invalid=true and aria-describedby linked to error element</t>
+        </is>
+      </c>
+      <c r="F78" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G78" s="44" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H78" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I78" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J78" s="44" t="inlineStr"/>
+      <c r="K78" s="44" t="inlineStr"/>
+      <c r="L78" s="44" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-080</t>
+        </is>
+      </c>
+      <c r="B79" s="44" t="inlineStr">
+        <is>
+          <t>F. Submission</t>
+        </is>
+      </c>
+      <c r="C79" s="44" t="inlineStr">
+        <is>
+          <t>Valid form submit</t>
+        </is>
+      </c>
+      <c r="D79" s="44" t="inlineStr">
+        <is>
+          <t>Fill all required fields + consent; submit</t>
+        </is>
+      </c>
+      <c r="E79" s="44" t="inlineStr">
+        <is>
+          <t>POST to /api/generic-submissions/submit; success toast; form resets</t>
+        </is>
+      </c>
+      <c r="F79" s="44" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G79" s="44" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H79" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01, PRE-02</t>
+        </is>
+      </c>
+      <c r="I79" s="44" t="inlineStr">
+        <is>
+          <t>Valid enquiry</t>
+        </is>
+      </c>
+      <c r="J79" s="44" t="inlineStr"/>
+      <c r="K79" s="44" t="inlineStr"/>
+      <c r="L79" s="44" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-081</t>
+        </is>
+      </c>
+      <c r="B80" s="44" t="inlineStr">
+        <is>
+          <t>F. Submission</t>
+        </is>
+      </c>
+      <c r="C80" s="44" t="inlineStr">
+        <is>
+          <t>Submit payload shape</t>
+        </is>
+      </c>
+      <c r="D80" s="44" t="inlineStr">
+        <is>
+          <t>Inspect network request on submit</t>
+        </is>
+      </c>
+      <c r="E80" s="44" t="inlineStr">
+        <is>
+          <t>JSON: formTag, fullName, phone (+code), email, reasonForContact, message, consentAccepted, sourcePage</t>
+        </is>
+      </c>
+      <c r="F80" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G80" s="44" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H80" s="44" t="inlineStr">
+        <is>
+          <t>PRE-02</t>
+        </is>
+      </c>
+      <c r="I80" s="44" t="inlineStr">
+        <is>
+          <t>Valid enquiry</t>
+        </is>
+      </c>
+      <c r="J80" s="44" t="inlineStr"/>
+      <c r="K80" s="44" t="inlineStr"/>
+      <c r="L80" s="44" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-082</t>
+        </is>
+      </c>
+      <c r="B81" s="44" t="inlineStr">
+        <is>
+          <t>F. Submission</t>
+        </is>
+      </c>
+      <c r="C81" s="44" t="inlineStr">
+        <is>
+          <t>Submit loading state</t>
+        </is>
+      </c>
+      <c r="D81" s="44" t="inlineStr">
+        <is>
+          <t>Submit valid form</t>
+        </is>
+      </c>
+      <c r="E81" s="44" t="inlineStr">
+        <is>
+          <t>Submit button disabled during isSubmitting</t>
+        </is>
+      </c>
+      <c r="F81" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G81" s="44" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="H81" s="44" t="inlineStr">
+        <is>
+          <t>PRE-02</t>
+        </is>
+      </c>
+      <c r="I81" s="44" t="inlineStr">
+        <is>
+          <t>Valid enquiry</t>
+        </is>
+      </c>
+      <c r="J81" s="44" t="inlineStr"/>
+      <c r="K81" s="44" t="inlineStr"/>
+      <c r="L81" s="44" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-083</t>
+        </is>
+      </c>
+      <c r="B82" s="44" t="inlineStr">
+        <is>
+          <t>F. Submission</t>
+        </is>
+      </c>
+      <c r="C82" s="44" t="inlineStr">
+        <is>
+          <t>Submit network failure</t>
+        </is>
+      </c>
+      <c r="D82" s="44" t="inlineStr">
+        <is>
+          <t>Block API; submit valid form</t>
+        </is>
+      </c>
+      <c r="E82" s="44" t="inlineStr">
+        <is>
+          <t>Destructive toast 'Unable to send message' with error detail</t>
+        </is>
+      </c>
+      <c r="F82" s="44" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G82" s="44" t="inlineStr">
+        <is>
+          <t>Resilience</t>
+        </is>
+      </c>
+      <c r="H82" s="44" t="inlineStr">
+        <is>
+          <t>PRE-02</t>
+        </is>
+      </c>
+      <c r="I82" s="44" t="inlineStr">
+        <is>
+          <t>Valid enquiry</t>
+        </is>
+      </c>
+      <c r="J82" s="44" t="inlineStr"/>
+      <c r="K82" s="44" t="inlineStr"/>
+      <c r="L82" s="44" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-084</t>
+        </is>
+      </c>
+      <c r="B83" s="44" t="inlineStr">
+        <is>
+          <t>F. Submission</t>
+        </is>
+      </c>
+      <c r="C83" s="44" t="inlineStr">
+        <is>
+          <t>Success message from CMS</t>
+        </is>
+      </c>
+      <c r="D83" s="44" t="inlineStr">
+        <is>
+          <t>Submit successfully</t>
+        </is>
+      </c>
+      <c r="E83" s="44" t="inlineStr">
+        <is>
+          <t>Toast shows CMS successMessage as description</t>
+        </is>
+      </c>
+      <c r="F83" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G83" s="44" t="inlineStr">
+        <is>
+          <t>CMS</t>
+        </is>
+      </c>
+      <c r="H83" s="44" t="inlineStr">
+        <is>
+          <t>PRE-02</t>
+        </is>
+      </c>
+      <c r="I83" s="44" t="inlineStr">
+        <is>
+          <t>Valid enquiry</t>
+        </is>
+      </c>
+      <c r="J83" s="44" t="inlineStr">
+        <is>
+          <t>No toast title on success</t>
+        </is>
+      </c>
+      <c r="K83" s="44" t="inlineStr"/>
+      <c r="L83" s="44" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-085</t>
+        </is>
+      </c>
+      <c r="B84" s="44" t="inlineStr">
+        <is>
+          <t>F. Submission</t>
+        </is>
+      </c>
+      <c r="C84" s="44" t="inlineStr">
+        <is>
+          <t>Form reset after success</t>
+        </is>
+      </c>
+      <c r="D84" s="44" t="inlineStr">
+        <is>
+          <t>Submit successfully</t>
+        </is>
+      </c>
+      <c r="E84" s="44" t="inlineStr">
+        <is>
+          <t>All fields cleared; consent unchecked</t>
+        </is>
+      </c>
+      <c r="F84" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G84" s="44" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H84" s="44" t="inlineStr">
+        <is>
+          <t>PRE-02</t>
+        </is>
+      </c>
+      <c r="I84" s="44" t="inlineStr">
+        <is>
+          <t>Valid enquiry</t>
+        </is>
+      </c>
+      <c r="J84" s="44" t="inlineStr">
+        <is>
+          <t>Country code resets to +91</t>
+        </is>
+      </c>
+      <c r="K84" s="44" t="inlineStr"/>
+      <c r="L84" s="44" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-086</t>
+        </is>
+      </c>
+      <c r="B85" s="44" t="inlineStr">
+        <is>
+          <t>F. Submission</t>
+        </is>
+      </c>
+      <c r="C85" s="44" t="inlineStr">
+        <is>
+          <t>Double submit prevention</t>
+        </is>
+      </c>
+      <c r="D85" s="44" t="inlineStr">
+        <is>
+          <t>Rapidly click submit twice</t>
+        </is>
+      </c>
+      <c r="E85" s="44" t="inlineStr">
+        <is>
+          <t>Only one submission sent</t>
+        </is>
+      </c>
+      <c r="F85" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G85" s="44" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H85" s="44" t="inlineStr">
+        <is>
+          <t>PRE-02</t>
+        </is>
+      </c>
+      <c r="I85" s="44" t="inlineStr">
+        <is>
+          <t>Valid enquiry</t>
+        </is>
+      </c>
+      <c r="J85" s="44" t="inlineStr"/>
+      <c r="K85" s="44" t="inlineStr"/>
+      <c r="L85" s="44" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-090</t>
+        </is>
+      </c>
+      <c r="B86" s="44" t="inlineStr">
+        <is>
+          <t>G. Consent</t>
+        </is>
+      </c>
+      <c r="C86" s="44" t="inlineStr">
+        <is>
+          <t>Consent checkbox renders</t>
+        </is>
+      </c>
+      <c r="D86" s="44" t="inlineStr">
+        <is>
+          <t>View consent row</t>
+        </is>
+      </c>
+      <c r="E86" s="44" t="inlineStr">
+        <is>
+          <t>Checkbox + CMS consent label with linked policies</t>
+        </is>
+      </c>
+      <c r="F86" s="44" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G86" s="44" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H86" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I86" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J86" s="44" t="inlineStr"/>
+      <c r="K86" s="44" t="inlineStr"/>
+      <c r="L86" s="44" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-091</t>
+        </is>
+      </c>
+      <c r="B87" s="44" t="inlineStr">
+        <is>
+          <t>G. Consent</t>
+        </is>
+      </c>
+      <c r="C87" s="44" t="inlineStr">
+        <is>
+          <t>Terms link navigation</t>
+        </is>
+      </c>
+      <c r="D87" s="44" t="inlineStr">
+        <is>
+          <t>Click TERMS &amp; CONDITIONS in consent</t>
+        </is>
+      </c>
+      <c r="E87" s="44" t="inlineStr">
+        <is>
+          <t>Navigates to /terms-and-conditions</t>
+        </is>
+      </c>
+      <c r="F87" s="44" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G87" s="44" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="H87" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I87" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J87" s="44" t="inlineStr"/>
+      <c r="K87" s="44" t="inlineStr"/>
+      <c r="L87" s="44" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-092</t>
+        </is>
+      </c>
+      <c r="B88" s="44" t="inlineStr">
+        <is>
+          <t>G. Consent</t>
+        </is>
+      </c>
+      <c r="C88" s="44" t="inlineStr">
+        <is>
+          <t>Privacy link navigation</t>
+        </is>
+      </c>
+      <c r="D88" s="44" t="inlineStr">
+        <is>
+          <t>Click PRIVACY POLICY in consent</t>
+        </is>
+      </c>
+      <c r="E88" s="44" t="inlineStr">
+        <is>
+          <t>Navigates to policy hub privacy-policy route</t>
+        </is>
+      </c>
+      <c r="F88" s="44" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G88" s="44" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="H88" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I88" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J88" s="44" t="inlineStr"/>
+      <c r="K88" s="44" t="inlineStr"/>
+      <c r="L88" s="44" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-093</t>
+        </is>
+      </c>
+      <c r="B89" s="44" t="inlineStr">
+        <is>
+          <t>G. Consent</t>
+        </is>
+      </c>
+      <c r="C89" s="44" t="inlineStr">
+        <is>
+          <t>Checkbox matches cart style</t>
+        </is>
+      </c>
+      <c r="D89" s="44" t="inlineStr">
+        <is>
+          <t>Compare checkbox with cart page</t>
+        </is>
+      </c>
+      <c r="E89" s="44" t="inlineStr">
+        <is>
+          <t>Same GiftingPanelCheckbox component/style</t>
+        </is>
+      </c>
+      <c r="F89" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G89" s="44" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="H89" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I89" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J89" s="44" t="inlineStr"/>
+      <c r="K89" s="44" t="inlineStr"/>
+      <c r="L89" s="44" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-094</t>
+        </is>
+      </c>
+      <c r="B90" s="44" t="inlineStr">
+        <is>
+          <t>G. Consent</t>
+        </is>
+      </c>
+      <c r="C90" s="44" t="inlineStr">
+        <is>
+          <t>Consent without label dead end</t>
+        </is>
+      </c>
+      <c r="D90" s="44" t="inlineStr">
+        <is>
+          <t>CMS: requiresConsent=true, consentLabel empty</t>
+        </is>
+      </c>
+      <c r="E90" s="44" t="inlineStr">
+        <is>
+          <t>Consent UI hidden but submit permanently disabled</t>
+        </is>
+      </c>
+      <c r="F90" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G90" s="44" t="inlineStr">
+        <is>
+          <t>Edge Case</t>
+        </is>
+      </c>
+      <c r="H90" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I90" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J90" s="44" t="inlineStr">
+        <is>
+          <t>Known bug</t>
+        </is>
+      </c>
+      <c r="K90" s="44" t="inlineStr"/>
+      <c r="L90" s="44" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-100</t>
+        </is>
+      </c>
+      <c r="B91" s="44" t="inlineStr">
+        <is>
+          <t>H. Prefill</t>
+        </is>
+      </c>
+      <c r="C91" s="44" t="inlineStr">
+        <is>
+          <t>Logged-in prefill</t>
+        </is>
+      </c>
+      <c r="D91" s="44" t="inlineStr">
+        <is>
+          <t>Sign in; open /contact</t>
+        </is>
+      </c>
+      <c r="E91" s="44" t="inlineStr">
+        <is>
+          <t>Name, email, phone prefilled from Magento profile</t>
+        </is>
+      </c>
+      <c r="F91" s="44" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G91" s="44" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H91" s="44" t="inlineStr">
+        <is>
+          <t>PRE-05</t>
+        </is>
+      </c>
+      <c r="I91" s="44" t="inlineStr">
+        <is>
+          <t>Logged-in user</t>
+        </is>
+      </c>
+      <c r="J91" s="44" t="inlineStr"/>
+      <c r="K91" s="44" t="inlineStr"/>
+      <c r="L91" s="44" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-101</t>
+        </is>
+      </c>
+      <c r="B92" s="44" t="inlineStr">
+        <is>
+          <t>H. Prefill</t>
+        </is>
+      </c>
+      <c r="C92" s="44" t="inlineStr">
+        <is>
+          <t>Prefill does not overwrite typed data</t>
+        </is>
+      </c>
+      <c r="D92" s="44" t="inlineStr">
+        <is>
+          <t>Type in name before prefill loads</t>
+        </is>
+      </c>
+      <c r="E92" s="44" t="inlineStr">
+        <is>
+          <t>User-typed value preserved</t>
+        </is>
+      </c>
+      <c r="F92" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G92" s="44" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H92" s="44" t="inlineStr">
+        <is>
+          <t>PRE-05</t>
+        </is>
+      </c>
+      <c r="I92" s="44" t="inlineStr">
+        <is>
+          <t>Logged-in user</t>
+        </is>
+      </c>
+      <c r="J92" s="44" t="inlineStr"/>
+      <c r="K92" s="44" t="inlineStr"/>
+      <c r="L92" s="44" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-102</t>
+        </is>
+      </c>
+      <c r="B93" s="44" t="inlineStr">
+        <is>
+          <t>H. Prefill</t>
+        </is>
+      </c>
+      <c r="C93" s="44" t="inlineStr">
+        <is>
+          <t>Prefill once only</t>
+        </is>
+      </c>
+      <c r="D93" s="44" t="inlineStr">
+        <is>
+          <t>Clear a prefilled field after load</t>
+        </is>
+      </c>
+      <c r="E93" s="44" t="inlineStr">
+        <is>
+          <t>Field not re-filled from profile</t>
+        </is>
+      </c>
+      <c r="F93" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G93" s="44" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H93" s="44" t="inlineStr">
+        <is>
+          <t>PRE-05</t>
+        </is>
+      </c>
+      <c r="I93" s="44" t="inlineStr">
+        <is>
+          <t>Logged-in user</t>
+        </is>
+      </c>
+      <c r="J93" s="44" t="inlineStr"/>
+      <c r="K93" s="44" t="inlineStr"/>
+      <c r="L93" s="44" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-103</t>
+        </is>
+      </c>
+      <c r="B94" s="44" t="inlineStr">
+        <is>
+          <t>H. Prefill</t>
+        </is>
+      </c>
+      <c r="C94" s="44" t="inlineStr">
+        <is>
+          <t>Profile fetch failure</t>
+        </is>
+      </c>
+      <c r="D94" s="44" t="inlineStr">
+        <is>
+          <t>Simulate profile API failure while logged in</t>
+        </is>
+      </c>
+      <c r="E94" s="44" t="inlineStr">
+        <is>
+          <t>Form remains empty/editable; no blocking error</t>
+        </is>
+      </c>
+      <c r="F94" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G94" s="44" t="inlineStr">
+        <is>
+          <t>Resilience</t>
+        </is>
+      </c>
+      <c r="H94" s="44" t="inlineStr">
+        <is>
+          <t>PRE-05</t>
+        </is>
+      </c>
+      <c r="I94" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J94" s="44" t="inlineStr"/>
+      <c r="K94" s="44" t="inlineStr"/>
+      <c r="L94" s="44" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-110</t>
+        </is>
+      </c>
+      <c r="B95" s="44" t="inlineStr">
+        <is>
+          <t>I. Visit Us</t>
+        </is>
+      </c>
+      <c r="C95" s="44" t="inlineStr">
+        <is>
+          <t>Visit Us section renders</t>
+        </is>
+      </c>
+      <c r="D95" s="44" t="inlineStr">
+        <is>
+          <t>Scroll to bottom of page</t>
+        </is>
+      </c>
+      <c r="E95" s="44" t="inlineStr">
+        <is>
+          <t>Visit Us title, description, image, CTA visible</t>
+        </is>
+      </c>
+      <c r="F95" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G95" s="44" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H95" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I95" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J95" s="44" t="inlineStr"/>
+      <c r="K95" s="44" t="inlineStr"/>
+      <c r="L95" s="44" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-111</t>
+        </is>
+      </c>
+      <c r="B96" s="44" t="inlineStr">
+        <is>
+          <t>I. Visit Us</t>
+        </is>
+      </c>
+      <c r="C96" s="44" t="inlineStr">
+        <is>
+          <t>Visit Us hidden when inactive</t>
+        </is>
+      </c>
+      <c r="D96" s="44" t="inlineStr">
+        <is>
+          <t>Disable visitSection in CMS</t>
+        </is>
+      </c>
+      <c r="E96" s="44" t="inlineStr">
+        <is>
+          <t>Section omitted</t>
+        </is>
+      </c>
+      <c r="F96" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G96" s="44" t="inlineStr">
+        <is>
+          <t>CMS</t>
+        </is>
+      </c>
+      <c r="H96" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I96" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J96" s="44" t="inlineStr"/>
+      <c r="K96" s="44" t="inlineStr"/>
+      <c r="L96" s="44" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-112</t>
+        </is>
+      </c>
+      <c r="B97" s="44" t="inlineStr">
+        <is>
+          <t>I. Visit Us</t>
+        </is>
+      </c>
+      <c r="C97" s="44" t="inlineStr">
+        <is>
+          <t>Visit Us CTA</t>
+        </is>
+      </c>
+      <c r="D97" s="44" t="inlineStr">
+        <is>
+          <t>Click Visit Us CTA</t>
+        </is>
+      </c>
+      <c r="E97" s="44" t="inlineStr">
+        <is>
+          <t>Opens Book a Visit flow or store locator per CMS config</t>
+        </is>
+      </c>
+      <c r="F97" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G97" s="44" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H97" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I97" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J97" s="44" t="inlineStr"/>
+      <c r="K97" s="44" t="inlineStr"/>
+      <c r="L97" s="44" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-113</t>
+        </is>
+      </c>
+      <c r="B98" s="44" t="inlineStr">
+        <is>
+          <t>I. Visit Us</t>
+        </is>
+      </c>
+      <c r="C98" s="44" t="inlineStr">
+        <is>
+          <t>Shared PDP component</t>
+        </is>
+      </c>
+      <c r="D98" s="44" t="inlineStr">
+        <is>
+          <t>Compare with PDP Visit Us</t>
+        </is>
+      </c>
+      <c r="E98" s="44" t="inlineStr">
+        <is>
+          <t>Same ProductDetailVisitUsSection behavior</t>
+        </is>
+      </c>
+      <c r="F98" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G98" s="44" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="H98" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I98" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J98" s="44" t="inlineStr"/>
+      <c r="K98" s="44" t="inlineStr"/>
+      <c r="L98" s="44" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-120</t>
+        </is>
+      </c>
+      <c r="B99" s="44" t="inlineStr">
+        <is>
+          <t>J. SEO</t>
+        </is>
+      </c>
+      <c r="C99" s="44" t="inlineStr">
+        <is>
+          <t>Page title from CMS</t>
+        </is>
+      </c>
+      <c r="D99" s="44" t="inlineStr">
+        <is>
+          <t>View page source / meta</t>
+        </is>
+      </c>
+      <c r="E99" s="44" t="inlineStr">
+        <is>
+          <t>CMS metaTitle in &lt;title&gt;</t>
+        </is>
+      </c>
+      <c r="F99" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G99" s="44" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="H99" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I99" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J99" s="44" t="inlineStr">
+        <is>
+          <t>Verified: Contact Us | Sunny Diamonds</t>
+        </is>
+      </c>
+      <c r="K99" s="44" t="inlineStr"/>
+      <c r="L99" s="44" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-121</t>
+        </is>
+      </c>
+      <c r="B100" s="44" t="inlineStr">
+        <is>
+          <t>J. SEO</t>
+        </is>
+      </c>
+      <c r="C100" s="44" t="inlineStr">
+        <is>
+          <t>Meta description from CMS</t>
+        </is>
+      </c>
+      <c r="D100" s="44" t="inlineStr">
+        <is>
+          <t>Inspect meta description tag</t>
+        </is>
+      </c>
+      <c r="E100" s="44" t="inlineStr">
+        <is>
+          <t>CMS metaDescription rendered</t>
+        </is>
+      </c>
+      <c r="F100" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G100" s="44" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="H100" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I100" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J100" s="44" t="inlineStr"/>
+      <c r="K100" s="44" t="inlineStr"/>
+      <c r="L100" s="44" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-122</t>
+        </is>
+      </c>
+      <c r="B101" s="44" t="inlineStr">
+        <is>
+          <t>J. SEO</t>
+        </is>
+      </c>
+      <c r="C101" s="44" t="inlineStr">
+        <is>
+          <t>Canonical URL</t>
+        </is>
+      </c>
+      <c r="D101" s="44" t="inlineStr">
+        <is>
+          <t>Inspect canonical link</t>
+        </is>
+      </c>
+      <c r="E101" s="44" t="inlineStr">
+        <is>
+          <t>CMS canonical or /contact default</t>
+        </is>
+      </c>
+      <c r="F101" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G101" s="44" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="H101" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I101" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J101" s="44" t="inlineStr"/>
+      <c r="K101" s="44" t="inlineStr"/>
+      <c r="L101" s="44" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-123</t>
+        </is>
+      </c>
+      <c r="B102" s="44" t="inlineStr">
+        <is>
+          <t>J. SEO</t>
+        </is>
+      </c>
+      <c r="C102" s="44" t="inlineStr">
+        <is>
+          <t>OG image</t>
+        </is>
+      </c>
+      <c r="D102" s="44" t="inlineStr">
+        <is>
+          <t>Inspect og:image when configured</t>
+        </is>
+      </c>
+      <c r="E102" s="44" t="inlineStr">
+        <is>
+          <t>CMS ogImage URL in metadata</t>
+        </is>
+      </c>
+      <c r="F102" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G102" s="44" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="H102" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I102" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J102" s="44" t="inlineStr"/>
+      <c r="K102" s="44" t="inlineStr"/>
+      <c r="L102" s="44" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-124</t>
+        </is>
+      </c>
+      <c r="B103" s="44" t="inlineStr">
+        <is>
+          <t>J. SEO</t>
+        </is>
+      </c>
+      <c r="C103" s="44" t="inlineStr">
+        <is>
+          <t>Fallback metadata</t>
+        </is>
+      </c>
+      <c r="D103" s="44" t="inlineStr">
+        <is>
+          <t>CMS SEO fields empty</t>
+        </is>
+      </c>
+      <c r="E103" s="44" t="inlineStr">
+        <is>
+          <t>siteConfig defaults used</t>
+        </is>
+      </c>
+      <c r="F103" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G103" s="44" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="H103" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I103" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J103" s="44" t="inlineStr"/>
+      <c r="K103" s="44" t="inlineStr"/>
+      <c r="L103" s="44" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-130</t>
+        </is>
+      </c>
+      <c r="B104" s="44" t="inlineStr">
+        <is>
+          <t>K. Accessibility</t>
+        </is>
+      </c>
+      <c r="C104" s="44" t="inlineStr">
+        <is>
+          <t>Heading hierarchy</t>
+        </is>
+      </c>
+      <c r="D104" s="44" t="inlineStr">
+        <is>
+          <t>Inspect page structure</t>
+        </is>
+      </c>
+      <c r="E104" s="44" t="inlineStr">
+        <is>
+          <t>h1 hero, h2 form/cards/visit</t>
+        </is>
+      </c>
+      <c r="F104" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G104" s="44" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H104" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I104" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J104" s="44" t="inlineStr"/>
+      <c r="K104" s="44" t="inlineStr"/>
+      <c r="L104" s="44" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-131</t>
+        </is>
+      </c>
+      <c r="B105" s="44" t="inlineStr">
+        <is>
+          <t>K. Accessibility</t>
+        </is>
+      </c>
+      <c r="C105" s="44" t="inlineStr">
+        <is>
+          <t>Form field labels</t>
+        </is>
+      </c>
+      <c r="D105" s="44" t="inlineStr">
+        <is>
+          <t>Screen reader / accessibility tree</t>
+        </is>
+      </c>
+      <c r="E105" s="44" t="inlineStr">
+        <is>
+          <t>All inputs have associated labels</t>
+        </is>
+      </c>
+      <c r="F105" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G105" s="44" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H105" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I105" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J105" s="44" t="inlineStr"/>
+      <c r="K105" s="44" t="inlineStr"/>
+      <c r="L105" s="44" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-132</t>
+        </is>
+      </c>
+      <c r="B106" s="44" t="inlineStr">
+        <is>
+          <t>K. Accessibility</t>
+        </is>
+      </c>
+      <c r="C106" s="44" t="inlineStr">
+        <is>
+          <t>Mobile header account icon</t>
+        </is>
+      </c>
+      <c r="D106" s="44" t="inlineStr">
+        <is>
+          <t>On mobile, tap user icon in header</t>
+        </is>
+      </c>
+      <c r="E106" s="44" t="inlineStr">
+        <is>
+          <t>Should navigate to account/profile; aria-label matches destination</t>
+        </is>
+      </c>
+      <c r="F106" s="44" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G106" s="44" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H106" s="44" t="inlineStr">
+        <is>
+          <t>PRE-03</t>
+        </is>
+      </c>
+      <c r="I106" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J106" s="44" t="inlineStr">
+        <is>
+          <t>FAIL: links to /contact, label 'Account'</t>
+        </is>
+      </c>
+      <c r="K106" s="44" t="inlineStr"/>
+      <c r="L106" s="44" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-133</t>
+        </is>
+      </c>
+      <c r="B107" s="44" t="inlineStr">
+        <is>
+          <t>K. Accessibility</t>
+        </is>
+      </c>
+      <c r="C107" s="44" t="inlineStr">
+        <is>
+          <t>Keyboard form navigation</t>
+        </is>
+      </c>
+      <c r="D107" s="44" t="inlineStr">
+        <is>
+          <t>Tab through form fields and submit</t>
+        </is>
+      </c>
+      <c r="E107" s="44" t="inlineStr">
+        <is>
+          <t>Logical tab order; focus visible</t>
+        </is>
+      </c>
+      <c r="F107" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G107" s="44" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="H107" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I107" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J107" s="44" t="inlineStr"/>
+      <c r="K107" s="44" t="inlineStr"/>
+      <c r="L107" s="44" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-140</t>
+        </is>
+      </c>
+      <c r="B108" s="44" t="inlineStr">
+        <is>
+          <t>L. CMS Content</t>
+        </is>
+      </c>
+      <c r="C108" s="44" t="inlineStr">
+        <is>
+          <t>Email CTA text accuracy</t>
+        </is>
+      </c>
+      <c r="D108" s="44" t="inlineStr">
+        <is>
+          <t>Review Email Us card link text</t>
+        </is>
+      </c>
+      <c r="E108" s="44" t="inlineStr">
+        <is>
+          <t>Properly formatted email address as link label</t>
+        </is>
+      </c>
+      <c r="F108" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G108" s="44" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="H108" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I108" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J108" s="44" t="inlineStr">
+        <is>
+          <t>FAIL: GET INTOUCH@SUNNTDIAMONDS.COM</t>
+        </is>
+      </c>
+      <c r="K108" s="44" t="inlineStr"/>
+      <c r="L108" s="44" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-141</t>
+        </is>
+      </c>
+      <c r="B109" s="44" t="inlineStr">
+        <is>
+          <t>L. CMS Content</t>
+        </is>
+      </c>
+      <c r="C109" s="44" t="inlineStr">
+        <is>
+          <t>Spelling in card descriptions</t>
+        </is>
+      </c>
+      <c r="D109" s="44" t="inlineStr">
+        <is>
+          <t>Review all card copy</t>
+        </is>
+      </c>
+      <c r="E109" s="44" t="inlineStr">
+        <is>
+          <t>No spelling/grammar errors</t>
+        </is>
+      </c>
+      <c r="F109" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G109" s="44" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="H109" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I109" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J109" s="44" t="inlineStr">
+        <is>
+          <t>FAIL: 'assisstance' typo</t>
+        </is>
+      </c>
+      <c r="K109" s="44" t="inlineStr"/>
+      <c r="L109" s="44" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-142</t>
+        </is>
+      </c>
+      <c r="B110" s="44" t="inlineStr">
+        <is>
+          <t>L. CMS Content</t>
+        </is>
+      </c>
+      <c r="C110" s="44" t="inlineStr">
+        <is>
+          <t>WhatsApp CTA label</t>
+        </is>
+      </c>
+      <c r="D110" s="44" t="inlineStr">
+        <is>
+          <t>Review WhatsApp link text</t>
+        </is>
+      </c>
+      <c r="E110" s="44" t="inlineStr">
+        <is>
+          <t>User-friendly label (not generic 'Whatsapp')</t>
+        </is>
+      </c>
+      <c r="F110" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G110" s="44" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="H110" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I110" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J110" s="44" t="inlineStr"/>
+      <c r="K110" s="44" t="inlineStr"/>
+      <c r="L110" s="44" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-150</t>
+        </is>
+      </c>
+      <c r="B111" s="44" t="inlineStr">
+        <is>
+          <t>M. Architecture</t>
+        </is>
+      </c>
+      <c r="C111" s="44" t="inlineStr">
+        <is>
+          <t>BFF proxy for submit</t>
+        </is>
+      </c>
+      <c r="D111" s="44" t="inlineStr">
+        <is>
+          <t>Inspect submit network call</t>
+        </is>
+      </c>
+      <c r="E111" s="44" t="inlineStr">
+        <is>
+          <t>POST goes to /api/generic-submissions/submit (not direct Strapi)</t>
+        </is>
+      </c>
+      <c r="F111" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G111" s="44" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="H111" s="44" t="inlineStr">
+        <is>
+          <t>PRE-02</t>
+        </is>
+      </c>
+      <c r="I111" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J111" s="44" t="inlineStr"/>
+      <c r="K111" s="44" t="inlineStr"/>
+      <c r="L111" s="44" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-151</t>
+        </is>
+      </c>
+      <c r="B112" s="44" t="inlineStr">
+        <is>
+          <t>M. Architecture</t>
+        </is>
+      </c>
+      <c r="C112" s="44" t="inlineStr">
+        <is>
+          <t>Direct Strapi form fetch</t>
+        </is>
+      </c>
+      <c r="D112" s="44" t="inlineStr">
+        <is>
+          <t>Inspect generic-forms client call</t>
+        </is>
+      </c>
+      <c r="E112" s="44" t="inlineStr">
+        <is>
+          <t>Client calls Strapi directly for form refresh</t>
+        </is>
+      </c>
+      <c r="F112" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G112" s="44" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
+      <c r="H112" s="44" t="inlineStr">
+        <is>
+          <t>PRE-02</t>
+        </is>
+      </c>
+      <c r="I112" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J112" s="44" t="inlineStr">
+        <is>
+          <t>Inconsistent with BFF pattern</t>
+        </is>
+      </c>
+      <c r="K112" s="44" t="inlineStr"/>
+      <c r="L112" s="44" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-152</t>
+        </is>
+      </c>
+      <c r="B113" s="44" t="inlineStr">
+        <is>
+          <t>M. Architecture</t>
+        </is>
+      </c>
+      <c r="C113" s="44" t="inlineStr">
+        <is>
+          <t>No server-side validation on BFF</t>
+        </is>
+      </c>
+      <c r="D113" s="44" t="inlineStr">
+        <is>
+          <t>POST invalid payload to BFF</t>
+        </is>
+      </c>
+      <c r="E113" s="44" t="inlineStr">
+        <is>
+          <t>BFF proxies to Strapi without validation</t>
+        </is>
+      </c>
+      <c r="F113" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G113" s="44" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="H113" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I113" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J113" s="44" t="inlineStr"/>
+      <c r="K113" s="44" t="inlineStr"/>
+      <c r="L113" s="44" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-153</t>
+        </is>
+      </c>
+      <c r="B114" s="44" t="inlineStr">
+        <is>
+          <t>M. Architecture</t>
+        </is>
+      </c>
+      <c r="C114" s="44" t="inlineStr">
+        <is>
+          <t>No rate limiting</t>
+        </is>
+      </c>
+      <c r="D114" s="44" t="inlineStr">
+        <is>
+          <t>Rapid repeated submissions</t>
+        </is>
+      </c>
+      <c r="E114" s="44" t="inlineStr">
+        <is>
+          <t>No client or BFF rate limiting</t>
+        </is>
+      </c>
+      <c r="F114" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G114" s="44" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="H114" s="44" t="inlineStr">
+        <is>
+          <t>PRE-02</t>
+        </is>
+      </c>
+      <c r="I114" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J114" s="44" t="inlineStr"/>
+      <c r="K114" s="44" t="inlineStr"/>
+      <c r="L114" s="44" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-160</t>
+        </is>
+      </c>
+      <c r="B115" s="44" t="inlineStr">
+        <is>
+          <t>N. Known Gaps</t>
+        </is>
+      </c>
+      <c r="C115" s="44" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="D115" s="44" t="inlineStr">
+        <is>
+          <t>Search codebase for contact tests</t>
+        </is>
+      </c>
+      <c r="E115" s="44" t="inlineStr">
+        <is>
+          <t>No unit/e2e tests for contact module</t>
+        </is>
+      </c>
+      <c r="F115" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G115" s="44" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="H115" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I115" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J115" s="44" t="inlineStr"/>
+      <c r="K115" s="44" t="inlineStr"/>
+      <c r="L115" s="44" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-161</t>
+        </is>
+      </c>
+      <c r="B116" s="44" t="inlineStr">
+        <is>
+          <t>N. Known Gaps</t>
+        </is>
+      </c>
+      <c r="C116" s="44" t="inlineStr">
+        <is>
+          <t>Reason label without options</t>
+        </is>
+      </c>
+      <c r="D116" s="44" t="inlineStr">
+        <is>
+          <t>CMS reason label set, no dropdown options</t>
+        </is>
+      </c>
+      <c r="E116" s="44" t="inlineStr">
+        <is>
+          <t>Form permanently unsubmittable</t>
+        </is>
+      </c>
+      <c r="F116" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G116" s="44" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="H116" s="44" t="inlineStr">
+        <is>
+          <t>PRE-01</t>
+        </is>
+      </c>
+      <c r="I116" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J116" s="44" t="inlineStr"/>
+      <c r="K116" s="44" t="inlineStr"/>
+      <c r="L116" s="44" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-162</t>
+        </is>
+      </c>
+      <c r="B117" s="44" t="inlineStr">
+        <is>
+          <t>N. Known Gaps</t>
+        </is>
+      </c>
+      <c r="C117" s="44" t="inlineStr">
+        <is>
+          <t>Static content dead code</t>
+        </is>
+      </c>
+      <c r="D117" s="44" t="inlineStr">
+        <is>
+          <t>Check features/contact/data/content.ts usage</t>
+        </is>
+      </c>
+      <c r="E117" s="44" t="inlineStr">
+        <is>
+          <t>File not imported; CMS-only design confirmed</t>
+        </is>
+      </c>
+      <c r="F117" s="44" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="G117" s="44" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="H117" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I117" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J117" s="44" t="inlineStr"/>
+      <c r="K117" s="44" t="inlineStr"/>
+      <c r="L117" s="44" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A5:F5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" style="41" min="1" max="1"/>
+    <col width="12" customWidth="1" style="41" min="2" max="2"/>
+    <col width="14" customWidth="1" style="41" min="3" max="3"/>
+    <col width="36" customWidth="1" style="41" min="4" max="4"/>
+    <col width="48" customWidth="1" style="41" min="5" max="5"/>
+    <col width="10" customWidth="1" style="41" min="6" max="6"/>
+    <col width="12" customWidth="1" style="41" min="7" max="7"/>
+    <col width="10" customWidth="1" style="41" min="8" max="8"/>
+    <col width="14" customWidth="1" style="41" min="9" max="9"/>
+    <col width="12" customWidth="1" style="41" min="10" max="10"/>
+    <col width="30" customWidth="1" style="41" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="42" t="inlineStr">
+        <is>
+          <t>CONTACT US MODULE — ISSUES / GAPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Review Date:</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Total Issues:</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="42" t="inlineStr">
+        <is>
+          <t>ISSUE SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="42" t="inlineStr">
+        <is>
+          <t>ISSUES</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t>Issue ID</t>
+        </is>
+      </c>
+      <c r="B11" s="43" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="C11" s="43" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="D11" s="43" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="E11" s="43" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F11" s="43" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="G11" s="43" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="H11" s="43" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I11" s="43" t="inlineStr">
+        <is>
+          <t>Related TCs</t>
+        </is>
+      </c>
+      <c r="J11" s="43" t="inlineStr">
+        <is>
+          <t>Jira</t>
+        </is>
+      </c>
+      <c r="K11" s="43" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-ISSUE-001</t>
+        </is>
+      </c>
+      <c r="B12" s="44" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="C12" s="44" t="inlineStr">
+        <is>
+          <t>Validation UX</t>
+        </is>
+      </c>
+      <c r="D12" s="44" t="inlineStr">
+        <is>
+          <t>Submit button disabled when form is invalid</t>
+        </is>
+      </c>
+      <c r="E12" s="44" t="inlineStr">
+        <is>
+          <t>Submit uses disabled={isSubmitting || !isFormReady}, preventing users from clicking Submit on an empty form. PRD test #9 expects inline validation on empty submit. Users only see errors field-by-field on blur.</t>
+        </is>
+      </c>
+      <c r="F12" s="44" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G12" s="44" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="H12" s="44" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I12" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-060</t>
+        </is>
+      </c>
+      <c r="J12" s="44" t="inlineStr">
+        <is>
+          <t>SD-162</t>
+        </is>
+      </c>
+      <c r="K12" s="44" t="inlineStr">
+        <is>
+          <t>ContactFormSection.tsx line 418</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-ISSUE-002</t>
+        </is>
+      </c>
+      <c r="B13" s="44" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="C13" s="44" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D13" s="44" t="inlineStr">
+        <is>
+          <t>Phone and email placeholders show 'Full Name'</t>
+        </is>
+      </c>
+      <c r="E13" s="44" t="inlineStr">
+        <is>
+          <t>ContactFormSection reuses form.fields.fieldPlaceholder (mapped from name field only) for phone and email inputs instead of field-specific placeholders.</t>
+        </is>
+      </c>
+      <c r="F13" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G13" s="44" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="H13" s="44" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I13" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-046</t>
+        </is>
+      </c>
+      <c r="J13" s="44" t="inlineStr">
+        <is>
+          <t>SD-163</t>
+        </is>
+      </c>
+      <c r="K13" s="44" t="inlineStr">
+        <is>
+          <t>contact-page.mapper.ts maps only nameField.placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-ISSUE-003</t>
+        </is>
+      </c>
+      <c r="B14" s="44" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C14" s="44" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="D14" s="44" t="inlineStr">
+        <is>
+          <t>Mobile header user icon mislabeled and wrong destination</t>
+        </is>
+      </c>
+      <c r="E14" s="44" t="inlineStr">
+        <is>
+          <t>MobileHeaderBar links UserIcon to /contact with aria-label='Account'. Screen readers announce 'Account' but user lands on Contact Us.</t>
+        </is>
+      </c>
+      <c r="F14" s="44" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G14" s="44" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="H14" s="44" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I14" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-132</t>
+        </is>
+      </c>
+      <c r="J14" s="44" t="inlineStr">
+        <is>
+          <t>SD-164</t>
+        </is>
+      </c>
+      <c r="K14" s="44" t="inlineStr">
+        <is>
+          <t>MobileHeaderBar.tsx line 52</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-ISSUE-004</t>
+        </is>
+      </c>
+      <c r="B15" s="44" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="C15" s="44" t="inlineStr">
+        <is>
+          <t>Consent</t>
+        </is>
+      </c>
+      <c r="D15" s="44" t="inlineStr">
+        <is>
+          <t>Consent required but label missing creates dead end</t>
+        </is>
+      </c>
+      <c r="E15" s="44" t="inlineStr">
+        <is>
+          <t>If requiresConsent=true and consentLabel is empty, checkbox UI is hidden but isFormReady still requires consentAccepted. Submit stays permanently disabled.</t>
+        </is>
+      </c>
+      <c r="F15" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G15" s="44" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="H15" s="44" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I15" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-094</t>
+        </is>
+      </c>
+      <c r="J15" s="44" t="inlineStr">
+        <is>
+          <t>SD-165</t>
+        </is>
+      </c>
+      <c r="K15" s="44" t="inlineStr">
+        <is>
+          <t>PRD section 14 documents this edge case</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-ISSUE-005</t>
+        </is>
+      </c>
+      <c r="B16" s="44" t="inlineStr">
+        <is>
+          <t>CMS Content</t>
+        </is>
+      </c>
+      <c r="C16" s="44" t="inlineStr">
+        <is>
+          <t>Email card</t>
+        </is>
+      </c>
+      <c r="D16" s="44" t="inlineStr">
+        <is>
+          <t>Malformed email CTA text</t>
+        </is>
+      </c>
+      <c r="E16" s="44" t="inlineStr">
+        <is>
+          <t>Email Us card displays 'GET INTOUCH@SUNNTDIAMONDS.COM' instead of a properly formatted email address.</t>
+        </is>
+      </c>
+      <c r="F16" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G16" s="44" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="H16" s="44" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I16" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-140</t>
+        </is>
+      </c>
+      <c r="J16" s="44" t="inlineStr">
+        <is>
+          <t>SD-166</t>
+        </is>
+      </c>
+      <c r="K16" s="44" t="inlineStr">
+        <is>
+          <t>CMS configuration issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-ISSUE-006</t>
+        </is>
+      </c>
+      <c r="B17" s="44" t="inlineStr">
+        <is>
+          <t>CMS Content</t>
+        </is>
+      </c>
+      <c r="C17" s="44" t="inlineStr">
+        <is>
+          <t>Personal Concierge card</t>
+        </is>
+      </c>
+      <c r="D17" s="44" t="inlineStr">
+        <is>
+          <t>Spelling error in card description</t>
+        </is>
+      </c>
+      <c r="E17" s="44" t="inlineStr">
+        <is>
+          <t>Description reads 'Get quick assisstance from our dedicated member of our team' — typo and grammar issues.</t>
+        </is>
+      </c>
+      <c r="F17" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G17" s="44" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="H17" s="44" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I17" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-141</t>
+        </is>
+      </c>
+      <c r="J17" s="44" t="inlineStr">
+        <is>
+          <t>SD-167</t>
+        </is>
+      </c>
+      <c r="K17" s="44" t="inlineStr">
+        <is>
+          <t>CMS copy fix</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-ISSUE-007</t>
+        </is>
+      </c>
+      <c r="B18" s="44" t="inlineStr">
+        <is>
+          <t>Contact Cards</t>
+        </is>
+      </c>
+      <c r="C18" s="44" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D18" s="44" t="inlineStr">
+        <is>
+          <t>mobileTitle mapped but never rendered</t>
+        </is>
+      </c>
+      <c r="E18" s="44" t="inlineStr">
+        <is>
+          <t>contact-page.mapper sets mobileTitle for email cards but ContactInfoSection always renders card.title.</t>
+        </is>
+      </c>
+      <c r="F18" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G18" s="44" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="H18" s="44" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I18" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-032</t>
+        </is>
+      </c>
+      <c r="J18" s="44" t="inlineStr">
+        <is>
+          <t>SD-168</t>
+        </is>
+      </c>
+      <c r="K18" s="44" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-ISSUE-008</t>
+        </is>
+      </c>
+      <c r="B19" s="44" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
+      <c r="C19" s="44" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D19" s="44" t="inlineStr">
+        <is>
+          <t>Client-side direct Strapi call for generic-forms</t>
+        </is>
+      </c>
+      <c r="E19" s="44" t="inlineStr">
+        <is>
+          <t>getGenericFormByTag calls Strapi from browser via apiFetch instead of BFF. Exposes CMS URL; depends on CORS.</t>
+        </is>
+      </c>
+      <c r="F19" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G19" s="44" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
+      <c r="H19" s="44" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I19" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-151</t>
+        </is>
+      </c>
+      <c r="J19" s="44" t="inlineStr">
+        <is>
+          <t>SD-169</t>
+        </is>
+      </c>
+      <c r="K19" s="44" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-ISSUE-009</t>
+        </is>
+      </c>
+      <c r="B20" s="44" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="C20" s="44" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="D20" s="44" t="inlineStr">
+        <is>
+          <t>No maxlength on message textarea</t>
+        </is>
+      </c>
+      <c r="E20" s="44" t="inlineStr">
+        <is>
+          <t>500-char limit validated only on submit; user can type beyond limit without immediate feedback.</t>
+        </is>
+      </c>
+      <c r="F20" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G20" s="44" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="H20" s="44" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I20" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-075</t>
+        </is>
+      </c>
+      <c r="J20" s="44" t="inlineStr">
+        <is>
+          <t>SD-170</t>
+        </is>
+      </c>
+      <c r="K20" s="44" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-ISSUE-010</t>
+        </is>
+      </c>
+      <c r="B21" s="44" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="C21" s="44" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D21" s="44" t="inlineStr">
+        <is>
+          <t>consentAccepted always sent as true</t>
+        </is>
+      </c>
+      <c r="E21" s="44" t="inlineStr">
+        <is>
+          <t>Submit payload hardcodes consentAccepted: true regardless of CMS requiresConsent setting.</t>
+        </is>
+      </c>
+      <c r="F21" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G21" s="44" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="H21" s="44" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I21" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-081</t>
+        </is>
+      </c>
+      <c r="J21" s="44" t="inlineStr">
+        <is>
+          <t>SD-171</t>
+        </is>
+      </c>
+      <c r="K21" s="44" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-ISSUE-011</t>
+        </is>
+      </c>
+      <c r="B22" s="44" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="C22" s="44" t="inlineStr">
+        <is>
+          <t>Reset</t>
+        </is>
+      </c>
+      <c r="D22" s="44" t="inlineStr">
+        <is>
+          <t>Country code resets to +91 after successful submit</t>
+        </is>
+      </c>
+      <c r="E22" s="44" t="inlineStr">
+        <is>
+          <t>resetForm() always sets countryCode to +91; profile prefill flag resets so non-+91 users lose their code until remount.</t>
+        </is>
+      </c>
+      <c r="F22" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G22" s="44" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="H22" s="44" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I22" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-085</t>
+        </is>
+      </c>
+      <c r="J22" s="44" t="inlineStr">
+        <is>
+          <t>SD-172</t>
+        </is>
+      </c>
+      <c r="K22" s="44" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-ISSUE-012</t>
+        </is>
+      </c>
+      <c r="B23" s="44" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="C23" s="44" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="D23" s="44" t="inlineStr">
+        <is>
+          <t>Success toast has no title</t>
+        </is>
+      </c>
+      <c r="E23" s="44" t="inlineStr">
+        <is>
+          <t>Success path only passes description to toast; error toast includes title 'Unable to send message'.</t>
+        </is>
+      </c>
+      <c r="F23" s="44" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="G23" s="44" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="H23" s="44" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I23" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-084</t>
+        </is>
+      </c>
+      <c r="J23" s="44" t="inlineStr">
+        <is>
+          <t>SD-173</t>
+        </is>
+      </c>
+      <c r="K23" s="44" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-ISSUE-013</t>
+        </is>
+      </c>
+      <c r="B24" s="44" t="inlineStr">
+        <is>
+          <t>Contact Cards</t>
+        </is>
+      </c>
+      <c r="C24" s="44" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="D24" s="44" t="inlineStr">
+        <is>
+          <t>Duplicate Tailwind classes in ContactInfoSection</t>
+        </is>
+      </c>
+      <c r="E24" s="44" t="inlineStr">
+        <is>
+          <t>Section className includes md:px-10 twice (xl:px-[150px] md:px-10 md:px-10).</t>
+        </is>
+      </c>
+      <c r="F24" s="44" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="G24" s="44" t="inlineStr">
+        <is>
+          <t>Code Quality</t>
+        </is>
+      </c>
+      <c r="H24" s="44" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I24" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J24" s="44" t="inlineStr">
+        <is>
+          <t>SD-174</t>
+        </is>
+      </c>
+      <c r="K24" s="44" t="inlineStr">
+        <is>
+          <t>ContactInfoSection.tsx line 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-ISSUE-014</t>
+        </is>
+      </c>
+      <c r="B25" s="44" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="C25" s="44" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="D25" s="44" t="inlineStr">
+        <is>
+          <t>No automated tests for Contact Us module</t>
+        </is>
+      </c>
+      <c r="E25" s="44" t="inlineStr">
+        <is>
+          <t>No unit, integration, or e2e tests found for contact page, form, or submission.</t>
+        </is>
+      </c>
+      <c r="F25" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G25" s="44" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="H25" s="44" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I25" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-160</t>
+        </is>
+      </c>
+      <c r="J25" s="44" t="inlineStr">
+        <is>
+          <t>SD-175</t>
+        </is>
+      </c>
+      <c r="K25" s="44" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-ISSUE-015</t>
+        </is>
+      </c>
+      <c r="B26" s="44" t="inlineStr">
+        <is>
+          <t>Resilience</t>
+        </is>
+      </c>
+      <c r="C26" s="44" t="inlineStr">
+        <is>
+          <t>Error handling</t>
+        </is>
+      </c>
+      <c r="D26" s="44" t="inlineStr">
+        <is>
+          <t>CMS failure shows empty page without user message</t>
+        </is>
+      </c>
+      <c r="E26" s="44" t="inlineStr">
+        <is>
+          <t>getContactPage catch returns EMPTY_CONTACT_PAGE silently; no retry or error UI for users.</t>
+        </is>
+      </c>
+      <c r="F26" s="44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G26" s="44" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="H26" s="44" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I26" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-005</t>
+        </is>
+      </c>
+      <c r="J26" s="44" t="inlineStr">
+        <is>
+          <t>SD-176</t>
+        </is>
+      </c>
+      <c r="K26" s="44" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-ISSUE-016</t>
+        </is>
+      </c>
+      <c r="B27" s="44" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="C27" s="44" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="D27" s="44" t="inlineStr">
+        <is>
+          <t>Reason required with empty dropdown options</t>
+        </is>
+      </c>
+      <c r="E27" s="44" t="inlineStr">
+        <is>
+          <t>If CMS sets reason label but no options, reasonRequired=true and form cannot be submitted.</t>
+        </is>
+      </c>
+      <c r="F27" s="44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G27" s="44" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="H27" s="44" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I27" s="44" t="inlineStr">
+        <is>
+          <t>CONTACT-161</t>
+        </is>
+      </c>
+      <c r="J27" s="44" t="inlineStr">
+        <is>
+          <t>SD-177</t>
+        </is>
+      </c>
+      <c r="K27" s="44" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A10:F10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>